--- a/01_raw_data/4.1_SOCS/raw/input/D2.8.SVY.BIZZ.xlsx
+++ b/01_raw_data/4.1_SOCS/raw/input/D2.8.SVY.BIZZ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/spi/technical-work/SPI/01_raw_data/4.1_SOCS/raw/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/spi/technical-work/SPI-Zander/SPI/01_raw_data/4.1_SOCS/raw/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="586" documentId="13_ncr:1_{785F06A1-600C-43BF-BDD6-ED8E91CA7490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A82BEA04-2BFA-40CC-9172-B1CB001A8480}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="13_ncr:1_{785F06A1-600C-43BF-BDD6-ED8E91CA7490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EAB2AA2-C8C7-3C4D-9031-FABA0C187588}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{B1D4A2B0-B996-4285-8899-E61063B05042}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="1" xr2:uid="{B1D4A2B0-B996-4285-8899-E61063B05042}"/>
   </bookViews>
   <sheets>
     <sheet name="2020 DCS" sheetId="13" r:id="rId1"/>
@@ -3858,7 +3858,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -3867,13 +3867,31 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-https://anda.inec.gob.ec/anda/index.php/catalog/807
-https://anda.inec.gob.ec/anda/index.php/catalog#_r=&amp;collection=&amp;country=&amp;dtype=&amp;from=2007&amp;page=6&amp;ps=%3Cfont%20style%3D%22vertical-align%3A%20inherit%3B%22%3E%3Cfont%20style%3D%22vertical-align%3A%20inherit%3B%22%3E100%3C/font%3E%3C/font%3E&amp;sk=&amp;sort_by=titl&amp;sort_order=&amp;to=2020&amp;topic=&amp;view=s&amp;vk=</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">https://anda.inec.gob.ec/anda/index.php/catalog/807
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>https://anda.inec.gob.ec/anda/index.php/catalog#_r=&amp;collection=&amp;country=&amp;dtype=&amp;from=2007&amp;page=6&amp;ps=%3Cfont%20style%3D%22vertical-align%3A%20inherit%3B%22%3E%3Cfont%20style%3D%22vertical-align%3A%20inherit%3B%22%3E100%3C/font%3E%3C/font%3E&amp;sk=&amp;sort_by=titl&amp;sort_order=&amp;to=2020&amp;topic=&amp;view=s&amp;vk=</t>
         </r>
       </text>
     </comment>
@@ -11167,7 +11185,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11277,6 +11295,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -11543,10 +11574,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11847,12 +11874,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9256EC4E-6C2C-4160-AE98-831950984D9C}">
   <dimension ref="A1:AB192"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -11932,7 +11959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -11943,7 +11970,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -12029,7 +12056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -12115,7 +12142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -12201,7 +12228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -12287,7 +12314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -12373,7 +12400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -12459,7 +12486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -12545,7 +12572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -12631,7 +12658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -12717,7 +12744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -12803,7 +12830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -12889,7 +12916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -12975,7 +13002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -13061,7 +13088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -13147,7 +13174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -13233,7 +13260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -13319,7 +13346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -13405,7 +13432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -13491,7 +13518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -13577,7 +13604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -13663,7 +13690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -13749,7 +13776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -13835,7 +13862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -13921,7 +13948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -14007,7 +14034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -14093,7 +14120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -14179,7 +14206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -14265,7 +14292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -14351,7 +14378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -14437,7 +14464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -14523,7 +14550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -14609,7 +14636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -14695,7 +14722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -14781,7 +14808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -14867,7 +14894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -14953,7 +14980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -15039,7 +15066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -15125,7 +15152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -15211,7 +15238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -15297,7 +15324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -15383,7 +15410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -15469,7 +15496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -15555,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -15641,7 +15668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -15727,7 +15754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -15813,7 +15840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -15899,7 +15926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>76</v>
       </c>
@@ -15985,7 +16012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -16071,7 +16098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -16157,7 +16184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -16243,7 +16270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -16329,7 +16356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>81</v>
       </c>
@@ -16415,7 +16442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -16501,7 +16528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -16587,7 +16614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -16673,7 +16700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -16759,7 +16786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>86</v>
       </c>
@@ -16845,7 +16872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>87</v>
       </c>
@@ -16931,7 +16958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -17017,7 +17044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -17103,7 +17130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>90</v>
       </c>
@@ -17189,7 +17216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -17275,7 +17302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>92</v>
       </c>
@@ -17361,7 +17388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>93</v>
       </c>
@@ -17447,7 +17474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -17533,7 +17560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>95</v>
       </c>
@@ -17619,7 +17646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>96</v>
       </c>
@@ -17705,7 +17732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>97</v>
       </c>
@@ -17791,7 +17818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>98</v>
       </c>
@@ -17877,7 +17904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>99</v>
       </c>
@@ -17963,7 +17990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -18049,7 +18076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>101</v>
       </c>
@@ -18135,7 +18162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>102</v>
       </c>
@@ -18221,7 +18248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>103</v>
       </c>
@@ -18307,7 +18334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -18393,7 +18420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>105</v>
       </c>
@@ -18479,7 +18506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>106</v>
       </c>
@@ -18565,7 +18592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>107</v>
       </c>
@@ -18651,7 +18678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>108</v>
       </c>
@@ -18737,7 +18764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -18823,7 +18850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>110</v>
       </c>
@@ -18909,7 +18936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>111</v>
       </c>
@@ -18995,7 +19022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>112</v>
       </c>
@@ -19081,7 +19108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>113</v>
       </c>
@@ -19167,7 +19194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>114</v>
       </c>
@@ -19253,7 +19280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -19339,7 +19366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>116</v>
       </c>
@@ -19425,7 +19452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>117</v>
       </c>
@@ -19511,7 +19538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>118</v>
       </c>
@@ -19597,7 +19624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>119</v>
       </c>
@@ -19683,7 +19710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>120</v>
       </c>
@@ -19769,7 +19796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -19855,7 +19882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -19941,7 +19968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>123</v>
       </c>
@@ -20027,7 +20054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -20113,7 +20140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>125</v>
       </c>
@@ -20199,7 +20226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>126</v>
       </c>
@@ -20285,7 +20312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>127</v>
       </c>
@@ -20371,7 +20398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>128</v>
       </c>
@@ -20454,7 +20481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>129</v>
       </c>
@@ -20540,7 +20567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>130</v>
       </c>
@@ -20626,7 +20653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>131</v>
       </c>
@@ -20712,7 +20739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>132</v>
       </c>
@@ -20798,7 +20825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>133</v>
       </c>
@@ -20884,7 +20911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>134</v>
       </c>
@@ -20970,7 +20997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>135</v>
       </c>
@@ -21056,7 +21083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>136</v>
       </c>
@@ -21142,7 +21169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>137</v>
       </c>
@@ -21228,7 +21255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>138</v>
       </c>
@@ -21314,7 +21341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -21400,7 +21427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>140</v>
       </c>
@@ -21486,7 +21513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>141</v>
       </c>
@@ -21572,7 +21599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>142</v>
       </c>
@@ -21658,7 +21685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>143</v>
       </c>
@@ -21744,7 +21771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>144</v>
       </c>
@@ -21830,7 +21857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>145</v>
       </c>
@@ -21916,7 +21943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>146</v>
       </c>
@@ -22002,7 +22029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>147</v>
       </c>
@@ -22088,7 +22115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>148</v>
       </c>
@@ -22174,7 +22201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>149</v>
       </c>
@@ -22260,7 +22287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>150</v>
       </c>
@@ -22346,7 +22373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>151</v>
       </c>
@@ -22432,7 +22459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>152</v>
       </c>
@@ -22518,7 +22545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -22604,7 +22631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -22690,7 +22717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>155</v>
       </c>
@@ -22776,7 +22803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>156</v>
       </c>
@@ -22862,7 +22889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>157</v>
       </c>
@@ -22948,7 +22975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>158</v>
       </c>
@@ -23034,7 +23061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>159</v>
       </c>
@@ -23120,7 +23147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>160</v>
       </c>
@@ -23206,7 +23233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>161</v>
       </c>
@@ -23292,7 +23319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>162</v>
       </c>
@@ -23378,7 +23405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -23464,7 +23491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>164</v>
       </c>
@@ -23550,7 +23577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>165</v>
       </c>
@@ -23636,7 +23663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>166</v>
       </c>
@@ -23722,7 +23749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>167</v>
       </c>
@@ -23808,7 +23835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>168</v>
       </c>
@@ -23894,7 +23921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>169</v>
       </c>
@@ -23980,7 +24007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>170</v>
       </c>
@@ -24066,7 +24093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>171</v>
       </c>
@@ -24152,7 +24179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>172</v>
       </c>
@@ -24238,7 +24265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>173</v>
       </c>
@@ -24324,7 +24351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>174</v>
       </c>
@@ -24410,7 +24437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>175</v>
       </c>
@@ -24496,7 +24523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>176</v>
       </c>
@@ -24582,7 +24609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>177</v>
       </c>
@@ -24668,7 +24695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>178</v>
       </c>
@@ -24754,7 +24781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>179</v>
       </c>
@@ -24840,7 +24867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>180</v>
       </c>
@@ -24926,7 +24953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>181</v>
       </c>
@@ -25012,7 +25039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>182</v>
       </c>
@@ -25098,7 +25125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>183</v>
       </c>
@@ -25184,7 +25211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>184</v>
       </c>
@@ -25270,7 +25297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>185</v>
       </c>
@@ -25356,7 +25383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>186</v>
       </c>
@@ -25442,7 +25469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>187</v>
       </c>
@@ -25528,7 +25555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -25614,7 +25641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>189</v>
       </c>
@@ -25700,7 +25727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>190</v>
       </c>
@@ -25786,7 +25813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>191</v>
       </c>
@@ -25872,7 +25899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>192</v>
       </c>
@@ -25958,7 +25985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>193</v>
       </c>
@@ -26044,7 +26071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>194</v>
       </c>
@@ -26130,7 +26157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>195</v>
       </c>
@@ -26216,7 +26243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>196</v>
       </c>
@@ -26302,7 +26329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>197</v>
       </c>
@@ -26388,7 +26415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>198</v>
       </c>
@@ -26474,7 +26501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -26560,7 +26587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>200</v>
       </c>
@@ -26646,7 +26673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>201</v>
       </c>
@@ -26732,7 +26759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>202</v>
       </c>
@@ -26818,7 +26845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>203</v>
       </c>
@@ -26904,7 +26931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>204</v>
       </c>
@@ -26990,7 +27017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>205</v>
       </c>
@@ -27076,7 +27103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>206</v>
       </c>
@@ -27162,7 +27189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>207</v>
       </c>
@@ -27248,7 +27275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>208</v>
       </c>
@@ -27334,7 +27361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>209</v>
       </c>
@@ -27420,7 +27447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>210</v>
       </c>
@@ -27506,7 +27533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>211</v>
       </c>
@@ -27592,7 +27619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>212</v>
       </c>
@@ -27678,7 +27705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>213</v>
       </c>
@@ -27764,7 +27791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>214</v>
       </c>
@@ -27850,7 +27877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>215</v>
       </c>
@@ -27936,7 +27963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>216</v>
       </c>
@@ -28022,7 +28049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>217</v>
       </c>
@@ -28108,7 +28135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>218</v>
       </c>
@@ -28194,7 +28221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>219</v>
       </c>
@@ -28291,17 +28318,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D041658-F9FA-4D77-A12C-CF7E074E9F02}">
-  <dimension ref="A1:CG193"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:CH193"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.54296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="9.54296875" style="2" customWidth="1"/>
-    <col min="33" max="33" width="156.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" style="2" customWidth="1"/>
+    <col min="4" max="5" width="9.5" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="25" width="0" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="156.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D1" s="10" t="s">
         <v>220</v>
       </c>
@@ -28313,7 +28341,7 @@
       </c>
       <c r="G1" s="48"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B2" s="1">
         <v>1</v>
       </c>
@@ -28400,8 +28428,9 @@
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="17" t="s">
         <v>26</v>
@@ -28496,11 +28525,14 @@
       <c r="AF3" s="49">
         <v>2024</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AG3" s="49">
+        <v>2025</v>
+      </c>
+      <c r="AH3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -28589,12 +28621,13 @@
       <c r="AD4" s="50"/>
       <c r="AE4" s="50"/>
       <c r="AF4" s="50"/>
-      <c r="AG4" t="str">
-        <f>+IF($D4=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E4=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA4=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB4=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC4=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD4=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE4=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF4=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG4" s="50"/>
+      <c r="AH4" t="str">
+        <f>+IF($D4=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E4=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA4=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB4=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC4=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD4=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE4=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF4=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG4=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2009, 2015, </v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -28683,12 +28716,13 @@
       <c r="AD5" s="50"/>
       <c r="AE5" s="50"/>
       <c r="AF5" s="50"/>
-      <c r="AG5" t="str">
-        <f t="shared" ref="AG5:AG68" si="0">+IF($D5=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E5=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA5=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB5=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC5=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD5=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE5=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF5=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG5" s="50"/>
+      <c r="AH5" t="str">
+        <f t="shared" ref="AH5:AH68" si="0">+IF($D5=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E5=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA5=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB5=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC5=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD5=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE5=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF5=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG5=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -28777,12 +28811,13 @@
       <c r="AD6" s="50"/>
       <c r="AE6" s="50"/>
       <c r="AF6" s="50"/>
-      <c r="AG6" t="str">
+      <c r="AG6" s="50"/>
+      <c r="AH6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -28871,12 +28906,13 @@
       <c r="AD7" s="50"/>
       <c r="AE7" s="50"/>
       <c r="AF7" s="50"/>
-      <c r="AG7" t="str">
+      <c r="AG7" s="50"/>
+      <c r="AH7" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -28965,12 +29001,13 @@
       <c r="AD8" s="50"/>
       <c r="AE8" s="50"/>
       <c r="AF8" s="50"/>
-      <c r="AG8" t="str">
+      <c r="AG8" s="50"/>
+      <c r="AH8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -29059,12 +29096,13 @@
       <c r="AD9" s="50"/>
       <c r="AE9" s="50"/>
       <c r="AF9" s="50"/>
-      <c r="AG9" t="str">
+      <c r="AG9" s="50"/>
+      <c r="AH9" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, </v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -29153,12 +29191,13 @@
       <c r="AD10" s="50"/>
       <c r="AE10" s="50"/>
       <c r="AF10" s="50"/>
-      <c r="AG10" t="str">
+      <c r="AG10" s="50"/>
+      <c r="AH10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -29247,12 +29286,13 @@
       <c r="AD11" s="50"/>
       <c r="AE11" s="50"/>
       <c r="AF11" s="50"/>
-      <c r="AG11" t="str">
+      <c r="AG11" s="50"/>
+      <c r="AH11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -29341,12 +29381,13 @@
       <c r="AD12" s="50"/>
       <c r="AE12" s="50"/>
       <c r="AF12" s="50"/>
-      <c r="AG12" t="str">
+      <c r="AG12" s="50"/>
+      <c r="AH12" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, </v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -29435,12 +29476,13 @@
       <c r="AD13" s="50"/>
       <c r="AE13" s="50"/>
       <c r="AF13" s="50"/>
-      <c r="AG13" t="str">
+      <c r="AG13" s="50"/>
+      <c r="AH13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -29529,12 +29571,13 @@
       <c r="AD14" s="50"/>
       <c r="AE14" s="50"/>
       <c r="AF14" s="50"/>
-      <c r="AG14" t="str">
+      <c r="AG14" s="50"/>
+      <c r="AH14" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2016, </v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -29623,12 +29666,13 @@
       <c r="AD15" s="50"/>
       <c r="AE15" s="50"/>
       <c r="AF15" s="50"/>
-      <c r="AG15" t="str">
+      <c r="AG15" s="50"/>
+      <c r="AH15" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -29717,12 +29761,13 @@
       <c r="AD16" s="50"/>
       <c r="AE16" s="50"/>
       <c r="AF16" s="50"/>
-      <c r="AG16" t="str">
+      <c r="AG16" s="50"/>
+      <c r="AH16" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -29811,12 +29856,13 @@
       <c r="AD17" s="50"/>
       <c r="AE17" s="50"/>
       <c r="AF17" s="50"/>
-      <c r="AG17" t="str">
+      <c r="AG17" s="50"/>
+      <c r="AH17" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2004, 2018, </v>
       </c>
     </row>
-    <row r="18" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -29905,12 +29951,13 @@
       <c r="AD18" s="50"/>
       <c r="AE18" s="50"/>
       <c r="AF18" s="50"/>
-      <c r="AG18" t="str">
+      <c r="AG18" s="50"/>
+      <c r="AH18" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="19" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -29999,12 +30046,13 @@
       <c r="AD19" s="50"/>
       <c r="AE19" s="50"/>
       <c r="AF19" s="50"/>
-      <c r="AG19" t="str">
+      <c r="AG19" s="50"/>
+      <c r="AH19" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2010, </v>
       </c>
     </row>
-    <row r="20" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -30093,12 +30141,13 @@
       <c r="AD20" s="50"/>
       <c r="AE20" s="50"/>
       <c r="AF20" s="50"/>
-      <c r="AG20" t="str">
+      <c r="AG20" s="50"/>
+      <c r="AH20" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="21" spans="1:85" s="22" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:86" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -30187,11 +30236,11 @@
       <c r="AD21" s="50"/>
       <c r="AE21" s="50"/>
       <c r="AF21" s="50"/>
-      <c r="AG21" t="str">
+      <c r="AG21" s="50"/>
+      <c r="AH21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
-      <c r="AH21"/>
       <c r="AI21"/>
       <c r="AJ21"/>
       <c r="AK21"/>
@@ -30217,8 +30266,9 @@
       <c r="BE21"/>
       <c r="BF21"/>
       <c r="BG21"/>
+      <c r="BH21"/>
     </row>
-    <row r="22" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -30307,12 +30357,13 @@
       <c r="AD22" s="50"/>
       <c r="AE22" s="50"/>
       <c r="AF22" s="50"/>
-      <c r="AG22" t="str">
+      <c r="AG22" s="50"/>
+      <c r="AH22" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2009, </v>
       </c>
     </row>
-    <row r="23" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -30401,12 +30452,13 @@
       <c r="AD23" s="50"/>
       <c r="AE23" s="50"/>
       <c r="AF23" s="50"/>
-      <c r="AG23" t="str">
+      <c r="AG23" s="50"/>
+      <c r="AH23" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2005, </v>
       </c>
     </row>
-    <row r="24" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -30495,12 +30547,13 @@
       <c r="AD24" s="50"/>
       <c r="AE24" s="50"/>
       <c r="AF24" s="50"/>
-      <c r="AG24" t="str">
+      <c r="AG24" s="50"/>
+      <c r="AH24" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2009, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="25" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -30589,12 +30642,13 @@
       <c r="AD25" s="50"/>
       <c r="AE25" s="50"/>
       <c r="AF25" s="50"/>
-      <c r="AG25" t="str">
+      <c r="AG25" s="50"/>
+      <c r="AH25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1999, 2005, </v>
       </c>
     </row>
-    <row r="26" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -30683,12 +30737,13 @@
       <c r="AD26" s="50"/>
       <c r="AE26" s="50"/>
       <c r="AF26" s="50"/>
-      <c r="AG26" t="str">
+      <c r="AG26" s="50"/>
+      <c r="AH26" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2009, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="27" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -30777,11 +30832,11 @@
       <c r="AD27" s="50"/>
       <c r="AE27" s="50"/>
       <c r="AF27" s="50"/>
-      <c r="AG27" t="str">
+      <c r="AG27" s="50"/>
+      <c r="AH27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AH27" s="24"/>
       <c r="AI27" s="24"/>
       <c r="AJ27" s="24"/>
       <c r="AK27" s="24"/>
@@ -30833,8 +30888,9 @@
       <c r="CE27" s="24"/>
       <c r="CF27" s="24"/>
       <c r="CG27" s="24"/>
+      <c r="CH27" s="24"/>
     </row>
-    <row r="28" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -30923,12 +30979,13 @@
       <c r="AD28" s="50"/>
       <c r="AE28" s="50"/>
       <c r="AF28" s="50"/>
-      <c r="AG28" t="str">
+      <c r="AG28" s="50"/>
+      <c r="AH28" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:85" s="22" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:86" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>26</v>
       </c>
@@ -31017,11 +31074,11 @@
       <c r="AD29" s="50"/>
       <c r="AE29" s="50"/>
       <c r="AF29" s="50"/>
-      <c r="AG29" t="str">
+      <c r="AG29" s="50"/>
+      <c r="AH29" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
-      <c r="AH29" s="24"/>
       <c r="AI29" s="24"/>
       <c r="AJ29" s="24"/>
       <c r="AK29" s="24"/>
@@ -31073,8 +31130,9 @@
       <c r="CE29" s="24"/>
       <c r="CF29" s="24"/>
       <c r="CG29" s="24"/>
+      <c r="CH29" s="24"/>
     </row>
-    <row r="30" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -31163,12 +31221,13 @@
       <c r="AD30" s="50"/>
       <c r="AE30" s="50"/>
       <c r="AF30" s="50"/>
-      <c r="AG30" t="str">
+      <c r="AG30" s="50"/>
+      <c r="AH30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -31257,12 +31316,13 @@
       <c r="AD31" s="50"/>
       <c r="AE31" s="50"/>
       <c r="AF31" s="50"/>
-      <c r="AG31" t="str">
+      <c r="AG31" s="50"/>
+      <c r="AH31" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="32" spans="1:85" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:86" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -31351,12 +31411,13 @@
       <c r="AD32" s="50"/>
       <c r="AE32" s="50"/>
       <c r="AF32" s="50"/>
-      <c r="AG32" t="str">
+      <c r="AG32" s="50"/>
+      <c r="AH32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -31445,12 +31506,13 @@
       <c r="AD33" s="50"/>
       <c r="AE33" s="50"/>
       <c r="AF33" s="50"/>
-      <c r="AG33" t="str">
+      <c r="AG33" s="50"/>
+      <c r="AH33" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2010, 2014, </v>
       </c>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -31539,12 +31601,13 @@
       <c r="AD34" s="50"/>
       <c r="AE34" s="50"/>
       <c r="AF34" s="50"/>
-      <c r="AG34" t="str">
+      <c r="AG34" s="50"/>
+      <c r="AH34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -31633,12 +31696,13 @@
       <c r="AD35" s="50"/>
       <c r="AE35" s="50"/>
       <c r="AF35" s="50"/>
-      <c r="AG35" t="str">
+      <c r="AG35" s="50"/>
+      <c r="AH35" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2011, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="36" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -31727,12 +31791,13 @@
       <c r="AD36" s="50"/>
       <c r="AE36" s="50"/>
       <c r="AF36" s="50"/>
-      <c r="AG36" t="str">
+      <c r="AG36" s="50"/>
+      <c r="AH36" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2009, 2017, </v>
       </c>
     </row>
-    <row r="37" spans="1:59" s="22" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:60" s="22" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -31821,11 +31886,11 @@
       <c r="AD37" s="50"/>
       <c r="AE37" s="50"/>
       <c r="AF37" s="50"/>
-      <c r="AG37" t="str">
+      <c r="AG37" s="50"/>
+      <c r="AH37" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
-      <c r="AH37"/>
       <c r="AI37"/>
       <c r="AJ37"/>
       <c r="AK37"/>
@@ -31851,8 +31916,9 @@
       <c r="BE37"/>
       <c r="BF37"/>
       <c r="BG37"/>
+      <c r="BH37"/>
     </row>
-    <row r="38" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -31941,12 +32007,13 @@
       <c r="AD38" s="50"/>
       <c r="AE38" s="50"/>
       <c r="AF38" s="50"/>
-      <c r="AG38" t="str">
+      <c r="AG38" s="50"/>
+      <c r="AH38" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -32035,12 +32102,13 @@
       <c r="AD39" s="50"/>
       <c r="AE39" s="50"/>
       <c r="AF39" s="50"/>
-      <c r="AG39" t="str">
+      <c r="AG39" s="50"/>
+      <c r="AH39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -32129,12 +32197,13 @@
       <c r="AD40" s="50"/>
       <c r="AE40" s="50"/>
       <c r="AF40" s="50"/>
-      <c r="AG40" t="str">
+      <c r="AG40" s="50"/>
+      <c r="AH40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -32223,12 +32292,13 @@
       <c r="AD41" s="50"/>
       <c r="AE41" s="50"/>
       <c r="AF41" s="50"/>
-      <c r="AG41" t="str">
+      <c r="AG41" s="50"/>
+      <c r="AH41" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="42" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -32317,12 +32387,13 @@
       <c r="AD42" s="50"/>
       <c r="AE42" s="50"/>
       <c r="AF42" s="50"/>
-      <c r="AG42" t="str">
+      <c r="AG42" s="50"/>
+      <c r="AH42" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -32411,12 +32482,13 @@
       <c r="AD43" s="50"/>
       <c r="AE43" s="50"/>
       <c r="AF43" s="50"/>
-      <c r="AG43" t="str">
+      <c r="AG43" s="50"/>
+      <c r="AH43" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -32505,12 +32577,13 @@
       <c r="AD44" s="50"/>
       <c r="AE44" s="50"/>
       <c r="AF44" s="50"/>
-      <c r="AG44" t="str">
+      <c r="AG44" s="50"/>
+      <c r="AH44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -32599,12 +32672,13 @@
       <c r="AD45" s="50"/>
       <c r="AE45" s="50"/>
       <c r="AF45" s="50"/>
-      <c r="AG45" t="str">
+      <c r="AG45" s="50"/>
+      <c r="AH45" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -32693,12 +32767,13 @@
       <c r="AD46" s="50"/>
       <c r="AE46" s="50"/>
       <c r="AF46" s="50"/>
-      <c r="AG46" t="str">
+      <c r="AG46" s="50"/>
+      <c r="AH46" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -32787,12 +32862,13 @@
       <c r="AD47" s="50"/>
       <c r="AE47" s="50"/>
       <c r="AF47" s="50"/>
-      <c r="AG47" t="str">
+      <c r="AG47" s="50"/>
+      <c r="AH47" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="48" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -32881,12 +32957,13 @@
       <c r="AD48" s="50"/>
       <c r="AE48" s="50"/>
       <c r="AF48" s="50"/>
-      <c r="AG48" t="str">
+      <c r="AG48" s="50"/>
+      <c r="AH48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>46</v>
       </c>
@@ -32975,12 +33052,13 @@
       <c r="AD49" s="50"/>
       <c r="AE49" s="50"/>
       <c r="AF49" s="50"/>
-      <c r="AG49" t="str">
+      <c r="AG49" s="50"/>
+      <c r="AH49" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>47</v>
       </c>
@@ -33069,12 +33147,13 @@
       <c r="AD50" s="50"/>
       <c r="AE50" s="50"/>
       <c r="AF50" s="50"/>
-      <c r="AG50" t="str">
+      <c r="AG50" s="50"/>
+      <c r="AH50" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -33163,12 +33242,13 @@
       <c r="AD51" s="50"/>
       <c r="AE51" s="50"/>
       <c r="AF51" s="50"/>
-      <c r="AG51" t="str">
+      <c r="AG51" s="50"/>
+      <c r="AH51" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -33257,12 +33337,13 @@
       <c r="AD52" s="50"/>
       <c r="AE52" s="50"/>
       <c r="AF52" s="50"/>
-      <c r="AG52" t="str">
+      <c r="AG52" s="50"/>
+      <c r="AH52" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2013, 2015, </v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>50</v>
       </c>
@@ -33351,12 +33432,13 @@
       <c r="AD53" s="50"/>
       <c r="AE53" s="50"/>
       <c r="AF53" s="50"/>
-      <c r="AG53" t="str">
+      <c r="AG53" s="50"/>
+      <c r="AH53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>51</v>
       </c>
@@ -33445,12 +33527,13 @@
       <c r="AD54" s="50"/>
       <c r="AE54" s="50"/>
       <c r="AF54" s="50"/>
-      <c r="AG54" t="str">
+      <c r="AG54" s="50"/>
+      <c r="AH54" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>52</v>
       </c>
@@ -33539,12 +33622,13 @@
       <c r="AD55" s="50"/>
       <c r="AE55" s="50"/>
       <c r="AF55" s="50"/>
-      <c r="AG55" t="str">
+      <c r="AG55" s="50"/>
+      <c r="AH55" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>53</v>
       </c>
@@ -33633,12 +33717,13 @@
       <c r="AD56" s="50"/>
       <c r="AE56" s="50"/>
       <c r="AF56" s="50"/>
-      <c r="AG56" t="str">
+      <c r="AG56" s="50"/>
+      <c r="AH56" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, </v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>54</v>
       </c>
@@ -33727,12 +33812,13 @@
       <c r="AD57" s="50"/>
       <c r="AE57" s="50"/>
       <c r="AF57" s="50"/>
-      <c r="AG57" t="str">
+      <c r="AG57" s="50"/>
+      <c r="AH57" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>55</v>
       </c>
@@ -33821,12 +33907,13 @@
       <c r="AD58" s="50"/>
       <c r="AE58" s="50"/>
       <c r="AF58" s="50"/>
-      <c r="AG58" t="str">
+      <c r="AG58" s="50"/>
+      <c r="AH58" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>56</v>
       </c>
@@ -33915,12 +34002,13 @@
       <c r="AD59" s="50"/>
       <c r="AE59" s="50"/>
       <c r="AF59" s="50"/>
-      <c r="AG59" t="str">
+      <c r="AG59" s="50"/>
+      <c r="AH59" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>57</v>
       </c>
@@ -34015,12 +34103,13 @@
       <c r="AF60" s="50">
         <v>1</v>
       </c>
-      <c r="AG60" t="str">
+      <c r="AG60" s="50"/>
+      <c r="AH60" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2022, 2023, 2024, </v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>58</v>
       </c>
@@ -34109,12 +34198,13 @@
       <c r="AD61" s="50"/>
       <c r="AE61" s="50"/>
       <c r="AF61" s="50"/>
-      <c r="AG61" t="str">
+      <c r="AG61" s="50"/>
+      <c r="AH61" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, </v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>59</v>
       </c>
@@ -34203,12 +34293,13 @@
       <c r="AD62" s="50"/>
       <c r="AE62" s="50"/>
       <c r="AF62" s="50"/>
-      <c r="AG62" t="str">
+      <c r="AG62" s="50"/>
+      <c r="AH62" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>60</v>
       </c>
@@ -34297,12 +34388,13 @@
       <c r="AD63" s="50"/>
       <c r="AE63" s="50"/>
       <c r="AF63" s="50"/>
-      <c r="AG63" t="str">
+      <c r="AG63" s="50"/>
+      <c r="AH63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>61</v>
       </c>
@@ -34391,12 +34483,13 @@
       <c r="AD64" s="50"/>
       <c r="AE64" s="50"/>
       <c r="AF64" s="50"/>
-      <c r="AG64" t="str">
+      <c r="AG64" s="50"/>
+      <c r="AH64" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>62</v>
       </c>
@@ -34485,12 +34578,13 @@
       <c r="AD65" s="50"/>
       <c r="AE65" s="50"/>
       <c r="AF65" s="50"/>
-      <c r="AG65" t="str">
+      <c r="AG65" s="50"/>
+      <c r="AH65" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2013, 2015, </v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>63</v>
       </c>
@@ -34579,12 +34673,13 @@
       <c r="AD66" s="50"/>
       <c r="AE66" s="50"/>
       <c r="AF66" s="50"/>
-      <c r="AG66" t="str">
+      <c r="AG66" s="50"/>
+      <c r="AH66" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>64</v>
       </c>
@@ -34673,12 +34768,13 @@
       <c r="AD67" s="50"/>
       <c r="AE67" s="50"/>
       <c r="AF67" s="50"/>
-      <c r="AG67" t="str">
+      <c r="AG67" s="50"/>
+      <c r="AH67" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>65</v>
       </c>
@@ -34767,12 +34863,13 @@
       <c r="AD68" s="50"/>
       <c r="AE68" s="50"/>
       <c r="AF68" s="50"/>
-      <c r="AG68" t="str">
+      <c r="AG68" s="50"/>
+      <c r="AH68" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>66</v>
       </c>
@@ -34861,12 +34958,13 @@
       <c r="AD69" s="50"/>
       <c r="AE69" s="50"/>
       <c r="AF69" s="50"/>
-      <c r="AG69" t="str">
-        <f t="shared" ref="AG69:AG132" si="1">+IF($D69=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E69=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F69=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G69=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H69=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I69=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J69=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K69=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L69=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M69=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N69=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O69=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P69=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q69=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R69=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S69=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T69=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U69=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V69=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W69=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X69=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y69=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z69=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA69=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB69=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC69=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD69=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE69=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF69=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG69" s="50"/>
+      <c r="AH69" t="str">
+        <f t="shared" ref="AH69:AH132" si="1">+IF($D69=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E69=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F69=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G69=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H69=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I69=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J69=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K69=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L69=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M69=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N69=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O69=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P69=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q69=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R69=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S69=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T69=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U69=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V69=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W69=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X69=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y69=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z69=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA69=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB69=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC69=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD69=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE69=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF69=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG69=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>67</v>
       </c>
@@ -34955,12 +35053,13 @@
       <c r="AD70" s="50"/>
       <c r="AE70" s="50"/>
       <c r="AF70" s="50"/>
-      <c r="AG70" t="str">
+      <c r="AG70" s="50"/>
+      <c r="AH70" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2003, </v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>68</v>
       </c>
@@ -35049,12 +35148,13 @@
       <c r="AD71" s="50"/>
       <c r="AE71" s="50"/>
       <c r="AF71" s="50"/>
-      <c r="AG71" t="str">
+      <c r="AG71" s="50"/>
+      <c r="AH71" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>69</v>
       </c>
@@ -35143,12 +35243,13 @@
       <c r="AD72" s="50"/>
       <c r="AE72" s="50"/>
       <c r="AF72" s="50"/>
-      <c r="AG72" t="str">
+      <c r="AG72" s="50"/>
+      <c r="AH72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>70</v>
       </c>
@@ -35237,12 +35338,13 @@
       <c r="AD73" s="50"/>
       <c r="AE73" s="50"/>
       <c r="AF73" s="50"/>
-      <c r="AG73" t="str">
+      <c r="AG73" s="50"/>
+      <c r="AH73" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>71</v>
       </c>
@@ -35331,12 +35433,13 @@
       <c r="AD74" s="50"/>
       <c r="AE74" s="50"/>
       <c r="AF74" s="50"/>
-      <c r="AG74" t="str">
+      <c r="AG74" s="50"/>
+      <c r="AH74" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>72</v>
       </c>
@@ -35425,12 +35528,13 @@
       <c r="AD75" s="50"/>
       <c r="AE75" s="50"/>
       <c r="AF75" s="50"/>
-      <c r="AG75" t="str">
+      <c r="AG75" s="50"/>
+      <c r="AH75" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:33" s="24" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:34" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>73</v>
       </c>
@@ -35519,12 +35623,13 @@
       <c r="AD76" s="50"/>
       <c r="AE76" s="50"/>
       <c r="AF76" s="50"/>
-      <c r="AG76" t="str">
+      <c r="AG76" s="50"/>
+      <c r="AH76" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2002, 2005, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>74</v>
       </c>
@@ -35613,12 +35718,13 @@
       <c r="AD77" s="50"/>
       <c r="AE77" s="50"/>
       <c r="AF77" s="50"/>
-      <c r="AG77" t="str">
+      <c r="AG77" s="50"/>
+      <c r="AH77" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>75</v>
       </c>
@@ -35707,12 +35813,13 @@
       <c r="AD78" s="50"/>
       <c r="AE78" s="50"/>
       <c r="AF78" s="50"/>
-      <c r="AG78" t="str">
+      <c r="AG78" s="50"/>
+      <c r="AH78" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1998, 2003, 2005, 2007, 2010, 2011, 2012, 2013, </v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>76</v>
       </c>
@@ -35801,12 +35908,13 @@
       <c r="AD79" s="50"/>
       <c r="AE79" s="50"/>
       <c r="AF79" s="50"/>
-      <c r="AG79" t="str">
+      <c r="AG79" s="50"/>
+      <c r="AH79" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2017, </v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>77</v>
       </c>
@@ -35895,12 +36003,13 @@
       <c r="AD80" s="50"/>
       <c r="AE80" s="50"/>
       <c r="AF80" s="50"/>
-      <c r="AG80" t="str">
+      <c r="AG80" s="50"/>
+      <c r="AH80" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2007, 2013, </v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>78</v>
       </c>
@@ -35989,12 +36098,13 @@
       <c r="AD81" s="50"/>
       <c r="AE81" s="50"/>
       <c r="AF81" s="50"/>
-      <c r="AG81" t="str">
+      <c r="AG81" s="50"/>
+      <c r="AH81" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2006, 2007, </v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>79</v>
       </c>
@@ -36083,12 +36193,13 @@
       <c r="AD82" s="50"/>
       <c r="AE82" s="50"/>
       <c r="AF82" s="50"/>
-      <c r="AG82" t="str">
+      <c r="AG82" s="50"/>
+      <c r="AH82" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>80</v>
       </c>
@@ -36177,12 +36288,13 @@
       <c r="AD83" s="50"/>
       <c r="AE83" s="50"/>
       <c r="AF83" s="50"/>
-      <c r="AG83" t="str">
+      <c r="AG83" s="50"/>
+      <c r="AH83" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>81</v>
       </c>
@@ -36271,12 +36383,13 @@
       <c r="AD84" s="50"/>
       <c r="AE84" s="50"/>
       <c r="AF84" s="50"/>
-      <c r="AG84" t="str">
+      <c r="AG84" s="50"/>
+      <c r="AH84" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>82</v>
       </c>
@@ -36365,12 +36478,13 @@
       <c r="AD85" s="50"/>
       <c r="AE85" s="50"/>
       <c r="AF85" s="50"/>
-      <c r="AG85" t="str">
+      <c r="AG85" s="50"/>
+      <c r="AH85" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>83</v>
       </c>
@@ -36459,12 +36573,13 @@
       <c r="AD86" s="50"/>
       <c r="AE86" s="50"/>
       <c r="AF86" s="50"/>
-      <c r="AG86" t="str">
+      <c r="AG86" s="50"/>
+      <c r="AH86" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>84</v>
       </c>
@@ -36553,12 +36668,13 @@
       <c r="AD87" s="51"/>
       <c r="AE87" s="51"/>
       <c r="AF87" s="51"/>
-      <c r="AG87" t="str">
+      <c r="AG87" s="51"/>
+      <c r="AH87" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, </v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>85</v>
       </c>
@@ -36647,12 +36763,13 @@
       <c r="AD88" s="50"/>
       <c r="AE88" s="50"/>
       <c r="AF88" s="50"/>
-      <c r="AG88" t="str">
+      <c r="AG88" s="50"/>
+      <c r="AH88" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>86</v>
       </c>
@@ -36741,12 +36858,13 @@
       <c r="AD89" s="50"/>
       <c r="AE89" s="50"/>
       <c r="AF89" s="50"/>
-      <c r="AG89" t="str">
+      <c r="AG89" s="50"/>
+      <c r="AH89" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>87</v>
       </c>
@@ -36835,12 +36953,13 @@
       <c r="AD90" s="50"/>
       <c r="AE90" s="50"/>
       <c r="AF90" s="50"/>
-      <c r="AG90" t="str">
+      <c r="AG90" s="50"/>
+      <c r="AH90" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2019, </v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>88</v>
       </c>
@@ -36929,12 +37048,13 @@
       <c r="AD91" s="50"/>
       <c r="AE91" s="50"/>
       <c r="AF91" s="50"/>
-      <c r="AG91" t="str">
+      <c r="AG91" s="50"/>
+      <c r="AH91" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>89</v>
       </c>
@@ -37023,12 +37143,13 @@
       <c r="AD92" s="50"/>
       <c r="AE92" s="50"/>
       <c r="AF92" s="50"/>
-      <c r="AG92" t="str">
+      <c r="AG92" s="50"/>
+      <c r="AH92" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2015, 2017, </v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>90</v>
       </c>
@@ -37117,12 +37238,13 @@
       <c r="AD93" s="50"/>
       <c r="AE93" s="50"/>
       <c r="AF93" s="50"/>
-      <c r="AG93" t="str">
+      <c r="AG93" s="50"/>
+      <c r="AH93" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>91</v>
       </c>
@@ -37211,12 +37333,13 @@
       <c r="AD94" s="50"/>
       <c r="AE94" s="50"/>
       <c r="AF94" s="50"/>
-      <c r="AG94" t="str">
+      <c r="AG94" s="50"/>
+      <c r="AH94" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>92</v>
       </c>
@@ -37305,12 +37428,13 @@
       <c r="AD95" s="50"/>
       <c r="AE95" s="50"/>
       <c r="AF95" s="50"/>
-      <c r="AG95" t="str">
+      <c r="AG95" s="50"/>
+      <c r="AH95" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, </v>
       </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>93</v>
       </c>
@@ -37399,12 +37523,13 @@
       <c r="AD96" s="50"/>
       <c r="AE96" s="50"/>
       <c r="AF96" s="50"/>
-      <c r="AG96" t="str">
+      <c r="AG96" s="50"/>
+      <c r="AH96" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>94</v>
       </c>
@@ -37493,12 +37618,13 @@
       <c r="AD97" s="50"/>
       <c r="AE97" s="50"/>
       <c r="AF97" s="50"/>
-      <c r="AG97" t="str">
+      <c r="AG97" s="50"/>
+      <c r="AH97" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>95</v>
       </c>
@@ -37587,12 +37713,13 @@
       <c r="AD98" s="50"/>
       <c r="AE98" s="50"/>
       <c r="AF98" s="50"/>
-      <c r="AG98" t="str">
+      <c r="AG98" s="50"/>
+      <c r="AH98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>96</v>
       </c>
@@ -37681,12 +37808,13 @@
       <c r="AD99" s="50"/>
       <c r="AE99" s="50"/>
       <c r="AF99" s="50"/>
-      <c r="AG99" t="str">
+      <c r="AG99" s="50"/>
+      <c r="AH99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>97</v>
       </c>
@@ -37775,12 +37903,13 @@
       <c r="AD100" s="50"/>
       <c r="AE100" s="50"/>
       <c r="AF100" s="50"/>
-      <c r="AG100" t="str">
+      <c r="AG100" s="50"/>
+      <c r="AH100" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>98</v>
       </c>
@@ -37869,12 +37998,13 @@
       <c r="AD101" s="50"/>
       <c r="AE101" s="50"/>
       <c r="AF101" s="50"/>
-      <c r="AG101" t="str">
+      <c r="AG101" s="50"/>
+      <c r="AH101" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>99</v>
       </c>
@@ -37961,12 +38091,13 @@
       <c r="AD102" s="50"/>
       <c r="AE102" s="50"/>
       <c r="AF102" s="50"/>
-      <c r="AG102" t="str">
+      <c r="AG102" s="50"/>
+      <c r="AH102" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>100</v>
       </c>
@@ -38055,12 +38186,13 @@
       <c r="AD103" s="50"/>
       <c r="AE103" s="50"/>
       <c r="AF103" s="50"/>
-      <c r="AG103" t="str">
+      <c r="AG103" s="50"/>
+      <c r="AH103" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2015, 2016, </v>
       </c>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>101</v>
       </c>
@@ -38149,12 +38281,13 @@
       <c r="AD104" s="50"/>
       <c r="AE104" s="50"/>
       <c r="AF104" s="50"/>
-      <c r="AG104" t="str">
+      <c r="AG104" s="50"/>
+      <c r="AH104" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2001, 2004, 2006, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>102</v>
       </c>
@@ -38245,12 +38378,13 @@
       </c>
       <c r="AE105" s="50"/>
       <c r="AF105" s="50"/>
-      <c r="AG105" t="str">
+      <c r="AG105" s="50"/>
+      <c r="AH105" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2005, 2008, 2014, 2015, 2016, 2017, 2018, 2022, </v>
       </c>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>103</v>
       </c>
@@ -38339,12 +38473,13 @@
       <c r="AD106" s="50"/>
       <c r="AE106" s="50"/>
       <c r="AF106" s="50"/>
-      <c r="AG106" t="str">
+      <c r="AG106" s="50"/>
+      <c r="AH106" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>104</v>
       </c>
@@ -38433,12 +38568,13 @@
       <c r="AD107" s="50"/>
       <c r="AE107" s="50"/>
       <c r="AF107" s="50"/>
-      <c r="AG107" t="str">
+      <c r="AG107" s="50"/>
+      <c r="AH107" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>105</v>
       </c>
@@ -38527,12 +38663,13 @@
       <c r="AD108" s="50"/>
       <c r="AE108" s="50"/>
       <c r="AF108" s="50"/>
-      <c r="AG108" t="str">
+      <c r="AG108" s="50"/>
+      <c r="AH108" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2010, 2015, </v>
       </c>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>106</v>
       </c>
@@ -38621,12 +38758,13 @@
       <c r="AD109" s="50"/>
       <c r="AE109" s="50"/>
       <c r="AF109" s="50"/>
-      <c r="AG109" t="str">
+      <c r="AG109" s="50"/>
+      <c r="AH109" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>107</v>
       </c>
@@ -38715,12 +38853,13 @@
       <c r="AD110" s="50"/>
       <c r="AE110" s="50"/>
       <c r="AF110" s="50"/>
-      <c r="AG110" t="str">
+      <c r="AG110" s="50"/>
+      <c r="AH110" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2013, </v>
       </c>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>108</v>
       </c>
@@ -38809,12 +38948,13 @@
       <c r="AD111" s="50"/>
       <c r="AE111" s="50"/>
       <c r="AF111" s="50"/>
-      <c r="AG111" t="str">
+      <c r="AG111" s="50"/>
+      <c r="AH111" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>109</v>
       </c>
@@ -38903,12 +39043,13 @@
       <c r="AD112" s="50"/>
       <c r="AE112" s="50"/>
       <c r="AF112" s="50"/>
-      <c r="AG112" t="str">
+      <c r="AG112" s="50"/>
+      <c r="AH112" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2013, </v>
       </c>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>110</v>
       </c>
@@ -38997,12 +39138,13 @@
       <c r="AD113" s="50"/>
       <c r="AE113" s="50"/>
       <c r="AF113" s="50"/>
-      <c r="AG113" t="str">
+      <c r="AG113" s="50"/>
+      <c r="AH113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>111</v>
       </c>
@@ -39091,12 +39233,13 @@
       <c r="AD114" s="50"/>
       <c r="AE114" s="50"/>
       <c r="AF114" s="50"/>
-      <c r="AG114" t="str">
+      <c r="AG114" s="50"/>
+      <c r="AH114" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>112</v>
       </c>
@@ -39185,12 +39328,13 @@
       <c r="AD115" s="50"/>
       <c r="AE115" s="50"/>
       <c r="AF115" s="50"/>
-      <c r="AG115" t="str">
+      <c r="AG115" s="50"/>
+      <c r="AH115" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>113</v>
       </c>
@@ -39279,12 +39423,13 @@
       <c r="AD116" s="50"/>
       <c r="AE116" s="50"/>
       <c r="AF116" s="50"/>
-      <c r="AG116" t="str">
+      <c r="AG116" s="50"/>
+      <c r="AH116" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>114</v>
       </c>
@@ -39373,12 +39518,13 @@
       <c r="AD117" s="50"/>
       <c r="AE117" s="50"/>
       <c r="AF117" s="50"/>
-      <c r="AG117" t="str">
+      <c r="AG117" s="50"/>
+      <c r="AH117" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>115</v>
       </c>
@@ -39467,12 +39613,13 @@
       <c r="AD118" s="50"/>
       <c r="AE118" s="50"/>
       <c r="AF118" s="50"/>
-      <c r="AG118" t="str">
+      <c r="AG118" s="50"/>
+      <c r="AH118" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>116</v>
       </c>
@@ -39561,12 +39708,13 @@
       <c r="AD119" s="50"/>
       <c r="AE119" s="50"/>
       <c r="AF119" s="50"/>
-      <c r="AG119" t="str">
+      <c r="AG119" s="50"/>
+      <c r="AH119" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2010, </v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>117</v>
       </c>
@@ -39655,12 +39803,13 @@
       <c r="AD120" s="50"/>
       <c r="AE120" s="50"/>
       <c r="AF120" s="50"/>
-      <c r="AG120" t="str">
+      <c r="AG120" s="50"/>
+      <c r="AH120" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>118</v>
       </c>
@@ -39749,12 +39898,13 @@
       <c r="AD121" s="50"/>
       <c r="AE121" s="50"/>
       <c r="AF121" s="50"/>
-      <c r="AG121" t="str">
+      <c r="AG121" s="50"/>
+      <c r="AH121" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>119</v>
       </c>
@@ -39843,12 +39993,13 @@
       <c r="AD122" s="50"/>
       <c r="AE122" s="50"/>
       <c r="AF122" s="50"/>
-      <c r="AG122" t="str">
+      <c r="AG122" s="50"/>
+      <c r="AH122" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>120</v>
       </c>
@@ -39937,12 +40088,13 @@
       <c r="AD123" s="50"/>
       <c r="AE123" s="50"/>
       <c r="AF123" s="50"/>
-      <c r="AG123" t="str">
+      <c r="AG123" s="50"/>
+      <c r="AH123" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>121</v>
       </c>
@@ -40031,12 +40183,13 @@
       <c r="AD124" s="50"/>
       <c r="AE124" s="50"/>
       <c r="AF124" s="50"/>
-      <c r="AG124" t="str">
+      <c r="AG124" s="50"/>
+      <c r="AH124" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>122</v>
       </c>
@@ -40125,12 +40278,13 @@
       <c r="AD125" s="50"/>
       <c r="AE125" s="50"/>
       <c r="AF125" s="50"/>
-      <c r="AG125" t="str">
+      <c r="AG125" s="50"/>
+      <c r="AH125" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>123</v>
       </c>
@@ -40219,12 +40373,13 @@
       <c r="AD126" s="50"/>
       <c r="AE126" s="50"/>
       <c r="AF126" s="50"/>
-      <c r="AG126" t="str">
+      <c r="AG126" s="50"/>
+      <c r="AH126" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>124</v>
       </c>
@@ -40313,12 +40468,13 @@
       <c r="AD127" s="50"/>
       <c r="AE127" s="50"/>
       <c r="AF127" s="50"/>
-      <c r="AG127" t="str">
+      <c r="AG127" s="50"/>
+      <c r="AH127" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2002, </v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>125</v>
       </c>
@@ -40407,12 +40563,13 @@
       <c r="AD128" s="50"/>
       <c r="AE128" s="50"/>
       <c r="AF128" s="50"/>
-      <c r="AG128" t="str">
+      <c r="AG128" s="50"/>
+      <c r="AH128" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2010, 2014, </v>
       </c>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>126</v>
       </c>
@@ -40501,12 +40658,13 @@
       <c r="AD129" s="50"/>
       <c r="AE129" s="50"/>
       <c r="AF129" s="50"/>
-      <c r="AG129" t="str">
+      <c r="AG129" s="50"/>
+      <c r="AH129" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2016, </v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>127</v>
       </c>
@@ -40595,12 +40753,13 @@
       <c r="AD130" s="50"/>
       <c r="AE130" s="50"/>
       <c r="AF130" s="50"/>
-      <c r="AG130" t="str">
+      <c r="AG130" s="50"/>
+      <c r="AH130" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>128</v>
       </c>
@@ -40689,12 +40848,13 @@
       <c r="AD131" s="50"/>
       <c r="AE131" s="50"/>
       <c r="AF131" s="50"/>
-      <c r="AG131" t="str">
+      <c r="AG131" s="50"/>
+      <c r="AH131" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>129</v>
       </c>
@@ -40783,12 +40943,13 @@
       <c r="AD132" s="50"/>
       <c r="AE132" s="50"/>
       <c r="AF132" s="50"/>
-      <c r="AG132" t="str">
+      <c r="AG132" s="50"/>
+      <c r="AH132" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>130</v>
       </c>
@@ -40877,12 +41038,13 @@
       <c r="AD133" s="50"/>
       <c r="AE133" s="50"/>
       <c r="AF133" s="50"/>
-      <c r="AG133" t="str">
-        <f t="shared" ref="AG133:AG193" si="2">+IF($D133=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E133=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F133=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G133=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H133=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I133=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J133=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K133=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L133=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M133=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N133=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O133=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P133=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q133=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R133=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S133=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T133=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U133=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V133=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W133=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X133=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y133=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z133=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA133=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB133=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC133=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD133=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE133=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF133=1, RIGHT(AF$3,4)&amp;", ", "")</f>
+      <c r="AG133" s="50"/>
+      <c r="AH133" t="str">
+        <f t="shared" ref="AH133:AH193" si="2">+IF($D133=1,RIGHT(D$3,4)&amp;", ","")&amp;IF($E133=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F133=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G133=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H133=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I133=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J133=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K133=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L133=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M133=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N133=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O133=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P133=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q133=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R133=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S133=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T133=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U133=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V133=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W133=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X133=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y133=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z133=1, RIGHT(Z$3,4)&amp;", ", "")&amp;IF($AA133=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB133=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC133=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD133=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE133=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF133=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG133=1, RIGHT(AG$3,4)&amp;", ", "")</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>131</v>
       </c>
@@ -40971,12 +41133,13 @@
       <c r="AD134" s="50"/>
       <c r="AE134" s="50"/>
       <c r="AF134" s="50"/>
-      <c r="AG134" t="str">
+      <c r="AG134" s="50"/>
+      <c r="AH134" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>132</v>
       </c>
@@ -41065,12 +41228,13 @@
       <c r="AD135" s="50"/>
       <c r="AE135" s="50"/>
       <c r="AF135" s="50"/>
-      <c r="AG135" t="str">
+      <c r="AG135" s="50"/>
+      <c r="AH135" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2011, 2012, 2013, 2014, 2015, 2016, </v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>133</v>
       </c>
@@ -41159,12 +41323,13 @@
       <c r="AD136" s="50"/>
       <c r="AE136" s="50"/>
       <c r="AF136" s="50"/>
-      <c r="AG136" t="str">
+      <c r="AG136" s="50"/>
+      <c r="AH136" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>134</v>
       </c>
@@ -41253,12 +41418,13 @@
       <c r="AD137" s="50"/>
       <c r="AE137" s="50"/>
       <c r="AF137" s="50"/>
-      <c r="AG137" t="str">
+      <c r="AG137" s="50"/>
+      <c r="AH137" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>135</v>
       </c>
@@ -41347,12 +41513,13 @@
       <c r="AD138" s="50"/>
       <c r="AE138" s="50"/>
       <c r="AF138" s="50"/>
-      <c r="AG138" t="str">
+      <c r="AG138" s="50"/>
+      <c r="AH138" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2006, </v>
       </c>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>136</v>
       </c>
@@ -41441,12 +41608,13 @@
       <c r="AD139" s="50"/>
       <c r="AE139" s="50"/>
       <c r="AF139" s="50"/>
-      <c r="AG139" t="str">
+      <c r="AG139" s="50"/>
+      <c r="AH139" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2002, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, </v>
       </c>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>137</v>
       </c>
@@ -41535,12 +41703,13 @@
       <c r="AD140" s="50"/>
       <c r="AE140" s="50"/>
       <c r="AF140" s="50"/>
-      <c r="AG140" t="str">
+      <c r="AG140" s="50"/>
+      <c r="AH140" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>138</v>
       </c>
@@ -41635,12 +41804,13 @@
         <v>1</v>
       </c>
       <c r="AF141" s="50"/>
-      <c r="AG141" t="str">
+      <c r="AG141" s="50"/>
+      <c r="AH141" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2002, 2019, 2021, 2022, 2023, </v>
       </c>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>139</v>
       </c>
@@ -41729,12 +41899,13 @@
       <c r="AD142" s="50"/>
       <c r="AE142" s="50"/>
       <c r="AF142" s="50"/>
-      <c r="AG142" t="str">
+      <c r="AG142" s="50"/>
+      <c r="AH142" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, </v>
       </c>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>140</v>
       </c>
@@ -41823,12 +41994,13 @@
       <c r="AD143" s="50"/>
       <c r="AE143" s="50"/>
       <c r="AF143" s="50"/>
-      <c r="AG143" t="str">
+      <c r="AG143" s="50"/>
+      <c r="AH143" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>141</v>
       </c>
@@ -41917,12 +42089,13 @@
       <c r="AD144" s="50"/>
       <c r="AE144" s="50"/>
       <c r="AF144" s="50"/>
-      <c r="AG144" t="str">
+      <c r="AG144" s="50"/>
+      <c r="AH144" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, </v>
       </c>
     </row>
-    <row r="145" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>142</v>
       </c>
@@ -42011,12 +42184,13 @@
       <c r="AD145" s="50"/>
       <c r="AE145" s="50"/>
       <c r="AF145" s="50"/>
-      <c r="AG145" t="str">
+      <c r="AG145" s="50"/>
+      <c r="AH145" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2004, </v>
       </c>
     </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>143</v>
       </c>
@@ -42105,12 +42279,13 @@
       <c r="AD146" s="50"/>
       <c r="AE146" s="50"/>
       <c r="AF146" s="50"/>
-      <c r="AG146" t="str">
+      <c r="AG146" s="50"/>
+      <c r="AH146" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>144</v>
       </c>
@@ -42199,12 +42374,13 @@
       <c r="AD147" s="50"/>
       <c r="AE147" s="50"/>
       <c r="AF147" s="50"/>
-      <c r="AG147" t="str">
+      <c r="AG147" s="50"/>
+      <c r="AH147" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>145</v>
       </c>
@@ -42293,12 +42469,13 @@
       <c r="AD148" s="50"/>
       <c r="AE148" s="50"/>
       <c r="AF148" s="50"/>
-      <c r="AG148" t="str">
+      <c r="AG148" s="50"/>
+      <c r="AH148" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="149" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>146</v>
       </c>
@@ -42389,15 +42566,16 @@
       <c r="AD149" s="18"/>
       <c r="AE149" s="50"/>
       <c r="AF149" s="50"/>
-      <c r="AG149" t="str">
+      <c r="AG149" s="50"/>
+      <c r="AH149" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2006, </v>
       </c>
-      <c r="AH149" s="31" t="s">
+      <c r="AI149" s="31" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>147</v>
       </c>
@@ -42488,15 +42666,16 @@
       <c r="AD150" s="18"/>
       <c r="AE150" s="50"/>
       <c r="AF150" s="50"/>
-      <c r="AG150" t="str">
+      <c r="AG150" s="50"/>
+      <c r="AH150" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2010, </v>
       </c>
-      <c r="AH150" s="29" t="s">
+      <c r="AI150" s="29" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>148</v>
       </c>
@@ -42587,18 +42766,19 @@
       <c r="AD151" s="18"/>
       <c r="AE151" s="50"/>
       <c r="AF151" s="50"/>
-      <c r="AG151" t="str">
+      <c r="AG151" s="50"/>
+      <c r="AH151" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH151" s="40" t="s">
+      <c r="AI151" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="AI151" s="33" t="s">
+      <c r="AJ151" s="33" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>149</v>
       </c>
@@ -42689,18 +42869,19 @@
       <c r="AD152" s="18"/>
       <c r="AE152" s="50"/>
       <c r="AF152" s="50"/>
-      <c r="AG152" t="str">
+      <c r="AG152" s="50"/>
+      <c r="AH152" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH152" s="40" t="s">
+      <c r="AI152" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="AI152" s="33" t="s">
+      <c r="AJ152" s="33" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="153" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>150</v>
       </c>
@@ -42791,15 +42972,16 @@
       <c r="AD153" s="18"/>
       <c r="AE153" s="50"/>
       <c r="AF153" s="50"/>
-      <c r="AG153" t="str">
+      <c r="AG153" s="50"/>
+      <c r="AH153" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH153" s="40" t="s">
+      <c r="AI153" s="40" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>151</v>
       </c>
@@ -42890,18 +43072,19 @@
       <c r="AD154" s="18"/>
       <c r="AE154" s="50"/>
       <c r="AF154" s="50"/>
-      <c r="AG154" t="str">
+      <c r="AG154" s="50"/>
+      <c r="AH154" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH154" s="40" t="s">
+      <c r="AI154" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="AI154" t="s">
+      <c r="AJ154" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>152</v>
       </c>
@@ -42992,18 +43175,19 @@
       <c r="AD155" s="18"/>
       <c r="AE155" s="50"/>
       <c r="AF155" s="50"/>
-      <c r="AG155" t="str">
+      <c r="AG155" s="50"/>
+      <c r="AH155" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH155" s="40" t="s">
+      <c r="AI155" s="40" t="s">
         <v>386</v>
       </c>
-      <c r="AI155" s="33" t="s">
+      <c r="AJ155" s="33" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>153</v>
       </c>
@@ -43094,15 +43278,16 @@
       <c r="AD156" s="18"/>
       <c r="AE156" s="50"/>
       <c r="AF156" s="50"/>
-      <c r="AG156" t="str">
+      <c r="AG156" s="50"/>
+      <c r="AH156" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1998, 1999, 2000, 2001, </v>
       </c>
-      <c r="AH156" s="31" t="s">
+      <c r="AI156" s="31" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="157" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>154</v>
       </c>
@@ -43195,15 +43380,16 @@
       </c>
       <c r="AE157" s="50"/>
       <c r="AF157" s="50"/>
-      <c r="AG157" t="str">
+      <c r="AG157" s="50"/>
+      <c r="AH157" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AH157" s="31" t="s">
+      <c r="AI157" s="31" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>155</v>
       </c>
@@ -43294,18 +43480,19 @@
       <c r="AD158" s="18"/>
       <c r="AE158" s="50"/>
       <c r="AF158" s="50"/>
-      <c r="AG158" t="str">
+      <c r="AG158" s="50"/>
+      <c r="AH158" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH158" s="41" t="s">
+      <c r="AI158" s="41" t="s">
         <v>393</v>
       </c>
-      <c r="AI158" s="33" t="s">
+      <c r="AJ158" s="33" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>156</v>
       </c>
@@ -43396,12 +43583,13 @@
       <c r="AD159" s="18"/>
       <c r="AE159" s="50"/>
       <c r="AF159" s="50"/>
-      <c r="AG159" t="str">
+      <c r="AG159" s="50"/>
+      <c r="AH159" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>157</v>
       </c>
@@ -43492,12 +43680,13 @@
       <c r="AD160" s="18"/>
       <c r="AE160" s="50"/>
       <c r="AF160" s="50"/>
-      <c r="AG160" t="str">
+      <c r="AG160" s="50"/>
+      <c r="AH160" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>158</v>
       </c>
@@ -43590,15 +43779,16 @@
       <c r="AF161" s="50">
         <v>1</v>
       </c>
-      <c r="AG161" t="str">
+      <c r="AG161" s="50"/>
+      <c r="AH161" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH161" s="32" t="s">
+      <c r="AI161" s="32" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="162" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>159</v>
       </c>
@@ -43691,19 +43881,20 @@
       </c>
       <c r="AE162" s="18"/>
       <c r="AF162" s="50"/>
-      <c r="AG162" t="str">
+      <c r="AG162" s="50"/>
+      <c r="AH162" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AH162" s="32" t="s">
+      <c r="AI162" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="AI162" s="33"/>
-      <c r="AR162" s="32" t="s">
+      <c r="AJ162" s="33"/>
+      <c r="AS162" s="32" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="163" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>160</v>
       </c>
@@ -43794,18 +43985,19 @@
       <c r="AD163" s="18"/>
       <c r="AE163" s="18"/>
       <c r="AF163" s="50"/>
-      <c r="AG163" t="str">
+      <c r="AG163" s="50"/>
+      <c r="AH163" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH163" s="33" t="s">
+      <c r="AI163" s="33" t="s">
         <v>403</v>
       </c>
-      <c r="AI163" s="32" t="s">
+      <c r="AJ163" s="32" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="164" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>161</v>
       </c>
@@ -43894,12 +44086,13 @@
       <c r="AD164" s="50"/>
       <c r="AE164" s="50"/>
       <c r="AF164" s="50"/>
-      <c r="AG164" t="str">
+      <c r="AG164" s="50"/>
+      <c r="AH164" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2010, </v>
       </c>
     </row>
-    <row r="165" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>162</v>
       </c>
@@ -43992,15 +44185,16 @@
       <c r="AF165" s="50">
         <v>1</v>
       </c>
-      <c r="AG165" t="str">
+      <c r="AG165" s="50"/>
+      <c r="AH165" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2021, 2024, </v>
       </c>
-      <c r="AH165" s="32" t="s">
+      <c r="AI165" s="32" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="166" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>163</v>
       </c>
@@ -44097,24 +44291,25 @@
       <c r="AF166" s="50">
         <v>1</v>
       </c>
-      <c r="AG166" t="str">
+      <c r="AG166" s="50"/>
+      <c r="AH166" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
       </c>
-      <c r="AH166" s="33" t="s">
+      <c r="AI166" s="33" t="s">
         <v>409</v>
       </c>
-      <c r="AI166" s="32" t="s">
+      <c r="AJ166" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="AJ166" s="32" t="s">
+      <c r="AK166" s="32" t="s">
         <v>411</v>
       </c>
-      <c r="AK166" t="s">
+      <c r="AL166" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="167" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>164</v>
       </c>
@@ -44205,18 +44400,19 @@
       <c r="AD167" s="18"/>
       <c r="AE167" s="18"/>
       <c r="AF167" s="50"/>
-      <c r="AG167" t="str">
+      <c r="AG167" s="50"/>
+      <c r="AH167" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH167" s="33" t="s">
+      <c r="AI167" s="33" t="s">
         <v>414</v>
       </c>
-      <c r="AI167" s="33" t="s">
+      <c r="AJ167" s="33" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="168" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>165</v>
       </c>
@@ -44309,21 +44505,22 @@
       <c r="AF168" s="50">
         <v>1</v>
       </c>
-      <c r="AG168" t="str">
+      <c r="AG168" s="50"/>
+      <c r="AH168" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH168" s="33" t="s">
-        <v>417</v>
-      </c>
       <c r="AI168" s="33" t="s">
         <v>417</v>
       </c>
       <c r="AJ168" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="AK168" s="33" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="169" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>166</v>
       </c>
@@ -44414,24 +44611,27 @@
       <c r="AD169" s="50"/>
       <c r="AE169" s="50"/>
       <c r="AF169" s="50"/>
-      <c r="AG169" t="str">
+      <c r="AG169" s="50">
+        <v>1</v>
+      </c>
+      <c r="AH169" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
-      </c>
-      <c r="AH169" s="33" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2025, </v>
+      </c>
+      <c r="AI169" s="33" t="s">
         <v>420</v>
       </c>
-      <c r="AI169" s="33" t="s">
+      <c r="AJ169" s="33" t="s">
         <v>421</v>
       </c>
-      <c r="AJ169" s="33" t="s">
+      <c r="AK169" s="33" t="s">
         <v>422</v>
       </c>
-      <c r="AK169" t="s">
+      <c r="AL169" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="170" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>167</v>
       </c>
@@ -44524,24 +44724,25 @@
       <c r="AF170" s="50">
         <v>1</v>
       </c>
-      <c r="AG170" t="str">
+      <c r="AG170" s="50"/>
+      <c r="AH170" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH170" s="33" t="s">
+      <c r="AI170" s="33" t="s">
         <v>425</v>
       </c>
-      <c r="AI170" s="33" t="s">
+      <c r="AJ170" s="33" t="s">
         <v>426</v>
       </c>
-      <c r="AJ170" s="33" t="s">
+      <c r="AK170" s="33" t="s">
         <v>425</v>
       </c>
-      <c r="AK170" s="33" t="s">
+      <c r="AL170" s="33" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="171" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>168</v>
       </c>
@@ -44634,18 +44835,21 @@
       <c r="AF171" s="50">
         <v>1</v>
       </c>
-      <c r="AG171" t="str">
+      <c r="AG171" s="50">
+        <v>1</v>
+      </c>
+      <c r="AH171" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
-      </c>
-      <c r="AH171" s="33" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, 2025, </v>
+      </c>
+      <c r="AI171" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="AI171" s="33" t="s">
+      <c r="AJ171" s="33" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="172" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>169</v>
       </c>
@@ -44736,27 +44940,28 @@
       <c r="AD172" s="50"/>
       <c r="AE172" s="50"/>
       <c r="AF172" s="50"/>
-      <c r="AG172" t="str">
+      <c r="AG172" s="50"/>
+      <c r="AH172" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH172" s="33" t="s">
+      <c r="AI172" s="33" t="s">
         <v>432</v>
       </c>
-      <c r="AI172" s="33" t="s">
+      <c r="AJ172" s="33" t="s">
         <v>433</v>
       </c>
-      <c r="AJ172" s="33" t="s">
+      <c r="AK172" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="AK172" s="33" t="s">
+      <c r="AL172" s="33" t="s">
         <v>435</v>
       </c>
-      <c r="AL172" t="s">
+      <c r="AM172" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="173" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>170</v>
       </c>
@@ -44847,21 +45052,24 @@
       <c r="AD173" s="50"/>
       <c r="AE173" s="50"/>
       <c r="AF173" s="50"/>
-      <c r="AG173" t="str">
+      <c r="AG173" s="50">
+        <v>1</v>
+      </c>
+      <c r="AH173" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
-      </c>
-      <c r="AH173" s="33" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2025, </v>
+      </c>
+      <c r="AI173" s="33" t="s">
         <v>437</v>
       </c>
-      <c r="AI173" s="32" t="s">
+      <c r="AJ173" s="32" t="s">
         <v>438</v>
       </c>
-      <c r="AJ173" t="s">
+      <c r="AK173" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="174" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>171</v>
       </c>
@@ -44954,27 +45162,28 @@
       <c r="AF174" s="51">
         <v>1</v>
       </c>
-      <c r="AG174" t="str">
+      <c r="AG174" s="51"/>
+      <c r="AH174" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH174" s="33" t="s">
+      <c r="AI174" s="33" t="s">
         <v>441</v>
       </c>
-      <c r="AI174" s="33" t="s">
+      <c r="AJ174" s="33" t="s">
         <v>442</v>
       </c>
-      <c r="AJ174" t="s">
+      <c r="AK174" t="s">
         <v>443</v>
       </c>
-      <c r="AK174" t="s">
+      <c r="AL174" t="s">
         <v>444</v>
       </c>
-      <c r="AL174" t="s">
+      <c r="AM174" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="175" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>172</v>
       </c>
@@ -45071,30 +45280,31 @@
       <c r="AF175" s="50">
         <v>1</v>
       </c>
-      <c r="AG175" t="str">
+      <c r="AG175" s="50"/>
+      <c r="AH175" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
       </c>
-      <c r="AH175" s="34" t="s">
+      <c r="AI175" s="34" t="s">
         <v>447</v>
       </c>
-      <c r="AI175" s="34" t="s">
+      <c r="AJ175" s="34" t="s">
         <v>448</v>
       </c>
-      <c r="AJ175" s="34" t="s">
+      <c r="AK175" s="34" t="s">
         <v>449</v>
       </c>
-      <c r="AK175" s="34" t="s">
+      <c r="AL175" s="34" t="s">
         <v>450</v>
       </c>
-      <c r="AL175" s="34" t="s">
+      <c r="AM175" s="34" t="s">
         <v>451</v>
       </c>
-      <c r="AM175" t="s">
+      <c r="AN175" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="176" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>173</v>
       </c>
@@ -45185,21 +45395,22 @@
       <c r="AD176" s="50"/>
       <c r="AE176" s="50"/>
       <c r="AF176" s="50"/>
-      <c r="AG176" t="str">
+      <c r="AG176" s="50"/>
+      <c r="AH176" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2020, 2021, </v>
       </c>
-      <c r="AH176" s="33" t="s">
+      <c r="AI176" s="33" t="s">
         <v>454</v>
       </c>
-      <c r="AI176" s="33" t="s">
+      <c r="AJ176" s="33" t="s">
         <v>455</v>
       </c>
-      <c r="AJ176" s="32" t="s">
+      <c r="AK176" s="32" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="177" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>174</v>
       </c>
@@ -45290,21 +45501,22 @@
       <c r="AD177" s="50"/>
       <c r="AE177" s="50"/>
       <c r="AF177" s="50"/>
-      <c r="AG177" t="str">
+      <c r="AG177" s="50"/>
+      <c r="AH177" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH177" s="33" t="s">
+      <c r="AI177" s="33" t="s">
         <v>458</v>
       </c>
-      <c r="AI177" s="32" t="s">
+      <c r="AJ177" s="32" t="s">
         <v>459</v>
       </c>
-      <c r="AJ177" t="s">
+      <c r="AK177" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="178" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>175</v>
       </c>
@@ -45399,19 +45611,20 @@
         <v>1</v>
       </c>
       <c r="AF178" s="50"/>
-      <c r="AG178" t="str">
+      <c r="AG178" s="50"/>
+      <c r="AH178" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, </v>
       </c>
-      <c r="AH178" s="32" t="s">
+      <c r="AI178" s="32" t="s">
         <v>462</v>
       </c>
-      <c r="AI178" s="32" t="s">
+      <c r="AJ178" s="32" t="s">
         <v>463</v>
       </c>
-      <c r="AJ178" s="33"/>
+      <c r="AK178" s="33"/>
     </row>
-    <row r="179" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>176</v>
       </c>
@@ -45502,24 +45715,25 @@
       <c r="AD179" s="50"/>
       <c r="AE179" s="50"/>
       <c r="AF179" s="50"/>
-      <c r="AG179" t="str">
+      <c r="AG179" s="50"/>
+      <c r="AH179" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH179" s="32" t="s">
+      <c r="AI179" s="32" t="s">
         <v>465</v>
       </c>
-      <c r="AI179" t="s">
+      <c r="AJ179" t="s">
         <v>466</v>
       </c>
-      <c r="AJ179" t="s">
+      <c r="AK179" t="s">
         <v>467</v>
       </c>
-      <c r="AK179" t="s">
+      <c r="AL179" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="180" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>177</v>
       </c>
@@ -45616,27 +45830,28 @@
       <c r="AF180" s="50">
         <v>1</v>
       </c>
-      <c r="AG180" t="str">
+      <c r="AG180" s="50"/>
+      <c r="AH180" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
       </c>
-      <c r="AH180" s="32" t="s">
+      <c r="AI180" s="32" t="s">
         <v>470</v>
       </c>
-      <c r="AI180" s="32" t="s">
+      <c r="AJ180" s="32" t="s">
         <v>471</v>
       </c>
-      <c r="AJ180" s="32" t="s">
+      <c r="AK180" s="32" t="s">
         <v>472</v>
       </c>
-      <c r="AK180" t="s">
+      <c r="AL180" t="s">
         <v>473</v>
       </c>
-      <c r="AM180" s="32" t="s">
+      <c r="AN180" s="32" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="181" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>178</v>
       </c>
@@ -45731,21 +45946,22 @@
         <v>1</v>
       </c>
       <c r="AF181" s="50"/>
-      <c r="AG181" t="str">
+      <c r="AG181" s="50"/>
+      <c r="AH181" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, </v>
       </c>
-      <c r="AH181" s="33" t="s">
+      <c r="AI181" s="33" t="s">
         <v>476</v>
       </c>
-      <c r="AI181" t="s">
+      <c r="AJ181" t="s">
         <v>477</v>
       </c>
-      <c r="AJ181" t="s">
+      <c r="AK181" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="182" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>179</v>
       </c>
@@ -45836,15 +46052,16 @@
       <c r="AD182" s="50"/>
       <c r="AE182" s="50"/>
       <c r="AF182" s="50"/>
-      <c r="AG182" t="str">
+      <c r="AG182" s="50"/>
+      <c r="AH182" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
-      <c r="AH182" s="32" t="s">
+      <c r="AI182" s="32" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="183" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>180</v>
       </c>
@@ -45937,21 +46154,22 @@
       <c r="AF183" s="50">
         <v>1</v>
       </c>
-      <c r="AG183" t="str">
+      <c r="AG183" s="50"/>
+      <c r="AH183" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH183" s="32" t="s">
+      <c r="AI183" s="32" t="s">
         <v>481</v>
       </c>
-      <c r="AI183" s="32" t="s">
+      <c r="AJ183" s="32" t="s">
         <v>482</v>
       </c>
-      <c r="AJ183" s="32" t="s">
+      <c r="AK183" s="32" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="184" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>181</v>
       </c>
@@ -46042,27 +46260,28 @@
       <c r="AD184" s="50"/>
       <c r="AE184" s="50"/>
       <c r="AF184" s="50"/>
-      <c r="AG184" t="str">
+      <c r="AG184" s="50"/>
+      <c r="AH184" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, </v>
       </c>
-      <c r="AH184" s="33" t="s">
+      <c r="AI184" s="33" t="s">
         <v>484</v>
       </c>
-      <c r="AI184" s="32" t="s">
+      <c r="AJ184" s="32" t="s">
         <v>485</v>
       </c>
-      <c r="AJ184" s="32" t="s">
+      <c r="AK184" s="32" t="s">
         <v>486</v>
       </c>
-      <c r="AK184" s="32" t="s">
+      <c r="AL184" s="32" t="s">
         <v>487</v>
       </c>
-      <c r="AL184" s="32" t="s">
+      <c r="AM184" s="32" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="185" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>182</v>
       </c>
@@ -46155,24 +46374,25 @@
       <c r="AF185" s="51">
         <v>1</v>
       </c>
-      <c r="AG185" t="str">
+      <c r="AG185" s="51"/>
+      <c r="AH185" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH185" s="33" t="s">
+      <c r="AI185" s="33" t="s">
         <v>490</v>
       </c>
-      <c r="AI185" s="33" t="s">
+      <c r="AJ185" s="33" t="s">
         <v>491</v>
       </c>
-      <c r="AJ185" s="32" t="s">
+      <c r="AK185" s="32" t="s">
         <v>492</v>
       </c>
-      <c r="AK185" t="s">
+      <c r="AL185" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="186" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>183</v>
       </c>
@@ -46265,21 +46485,22 @@
       <c r="AF186" s="50">
         <v>1</v>
       </c>
-      <c r="AG186" t="str">
+      <c r="AG186" s="50"/>
+      <c r="AH186" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH186" s="33" t="s">
+      <c r="AI186" s="33" t="s">
         <v>495</v>
       </c>
-      <c r="AI186" s="33" t="s">
+      <c r="AJ186" s="33" t="s">
         <v>496</v>
       </c>
-      <c r="AJ186" s="32" t="s">
+      <c r="AK186" s="32" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="187" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>184</v>
       </c>
@@ -46372,24 +46593,27 @@
       <c r="AF187" s="50">
         <v>1</v>
       </c>
-      <c r="AG187" t="str">
+      <c r="AG187" s="50">
+        <v>1</v>
+      </c>
+      <c r="AH187" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
-      </c>
-      <c r="AH187" t="s">
+        <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, 2025, </v>
+      </c>
+      <c r="AI187" t="s">
         <v>499</v>
       </c>
-      <c r="AI187" s="33" t="s">
+      <c r="AJ187" s="33" t="s">
         <v>500</v>
       </c>
-      <c r="AJ187" t="s">
+      <c r="AK187" t="s">
         <v>501</v>
       </c>
-      <c r="AK187" t="s">
+      <c r="AL187" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="188" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>185</v>
       </c>
@@ -46482,21 +46706,22 @@
       <c r="AF188" s="50">
         <v>1</v>
       </c>
-      <c r="AG188" t="str">
+      <c r="AG188" s="50"/>
+      <c r="AH188" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH188" s="34" t="s">
+      <c r="AI188" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="AI188" s="39" t="s">
+      <c r="AJ188" s="39" t="s">
         <v>505</v>
       </c>
-      <c r="AJ188" t="s">
+      <c r="AK188" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="189" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>186</v>
       </c>
@@ -46591,18 +46816,19 @@
         <v>1</v>
       </c>
       <c r="AF189" s="50"/>
-      <c r="AG189" t="str">
+      <c r="AG189" s="50"/>
+      <c r="AH189" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, </v>
       </c>
-      <c r="AH189" s="33" t="s">
+      <c r="AI189" s="33" t="s">
         <v>508</v>
       </c>
-      <c r="AI189" t="s">
+      <c r="AJ189" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="190" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>187</v>
       </c>
@@ -46697,27 +46923,28 @@
         <v>1</v>
       </c>
       <c r="AF190" s="50"/>
-      <c r="AG190" t="str">
+      <c r="AG190" s="50"/>
+      <c r="AH190" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, </v>
       </c>
-      <c r="AH190" s="32" t="s">
+      <c r="AI190" s="32" t="s">
         <v>511</v>
       </c>
-      <c r="AI190" s="33" t="s">
+      <c r="AJ190" s="33" t="s">
         <v>512</v>
       </c>
-      <c r="AJ190" s="33" t="s">
+      <c r="AK190" s="33" t="s">
         <v>513</v>
       </c>
-      <c r="AK190" s="33" t="s">
+      <c r="AL190" s="33" t="s">
         <v>514</v>
       </c>
-      <c r="AL190" s="33" t="s">
+      <c r="AM190" s="33" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="191" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>188</v>
       </c>
@@ -46810,30 +47037,31 @@
       <c r="AF191" s="50">
         <v>1</v>
       </c>
-      <c r="AG191" t="str">
+      <c r="AG191" s="50"/>
+      <c r="AH191" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
       </c>
-      <c r="AH191" s="33" t="s">
+      <c r="AI191" s="33" t="s">
         <v>517</v>
       </c>
-      <c r="AI191" s="33" t="s">
+      <c r="AJ191" s="33" t="s">
         <v>518</v>
       </c>
-      <c r="AJ191" s="33" t="s">
+      <c r="AK191" s="33" t="s">
         <v>519</v>
       </c>
-      <c r="AK191" s="33" t="s">
+      <c r="AL191" s="33" t="s">
         <v>520</v>
       </c>
-      <c r="AL191" t="s">
+      <c r="AM191" t="s">
         <v>521</v>
       </c>
-      <c r="AM191" t="s">
+      <c r="AN191" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="192" spans="1:39" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>189</v>
       </c>
@@ -46926,27 +47154,30 @@
       <c r="AF192" s="50">
         <v>1</v>
       </c>
-      <c r="AG192" t="str">
+      <c r="AG192" s="50">
+        <v>1</v>
+      </c>
+      <c r="AH192" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, </v>
-      </c>
-      <c r="AH192" s="32" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2024, 2025, </v>
+      </c>
+      <c r="AI192" s="32" t="s">
         <v>524</v>
       </c>
-      <c r="AI192" s="32" t="s">
+      <c r="AJ192" s="32" t="s">
         <v>525</v>
       </c>
-      <c r="AJ192" s="32" t="s">
+      <c r="AK192" s="32" t="s">
         <v>526</v>
       </c>
-      <c r="AK192" s="32" t="s">
+      <c r="AL192" s="32" t="s">
         <v>527</v>
       </c>
-      <c r="AL192" s="32" t="s">
+      <c r="AM192" s="32" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="193" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>190</v>
       </c>
@@ -47043,118 +47274,121 @@
       <c r="AF193" s="50">
         <v>1</v>
       </c>
-      <c r="AG193" t="str">
+      <c r="AG193" s="50">
+        <v>1</v>
+      </c>
+      <c r="AH193" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AH193" s="32" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AI193" s="32" t="s">
         <v>530</v>
       </c>
-      <c r="AI193" s="32" t="s">
+      <c r="AJ193" s="32" t="s">
         <v>531</v>
       </c>
-      <c r="AJ193" s="32" t="s">
+      <c r="AK193" s="32" t="s">
         <v>532</v>
       </c>
-      <c r="AK193" t="s">
+      <c r="AL193" t="s">
         <v>533</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AH149" r:id="rId1" xr:uid="{52AC0ED7-7648-40F7-B571-616312535AAA}"/>
-    <hyperlink ref="AH157" r:id="rId2" xr:uid="{45571AB8-A194-4CB5-B86F-42770FE8F0EC}"/>
-    <hyperlink ref="AL190" r:id="rId3" xr:uid="{E1B26233-1D7F-4B6E-A7B3-316AF4DFD64D}"/>
-    <hyperlink ref="AI185" r:id="rId4" xr:uid="{865742E7-BC6D-48C2-8AD9-20E9F8A9CB8D}"/>
-    <hyperlink ref="AI187" r:id="rId5" xr:uid="{87635245-1906-4D40-9B72-2665339404C6}"/>
-    <hyperlink ref="AH161" r:id="rId6" xr:uid="{2BBA1E7B-3597-451D-BB1B-DA7942019B4E}"/>
-    <hyperlink ref="AH189" r:id="rId7" xr:uid="{5F662825-2BB5-45A8-B790-BE007838E78C}"/>
-    <hyperlink ref="AH177" r:id="rId8" xr:uid="{D5E1BC65-C3C1-4385-AF10-90A6F6274C3D}"/>
-    <hyperlink ref="AH163" r:id="rId9" location="documents" xr:uid="{56A02F04-D2F7-469A-87C0-53B8348EFE61}"/>
-    <hyperlink ref="AJ170" r:id="rId10" xr:uid="{EB7D60BA-0955-4550-B994-AEEAFCFB73F9}"/>
-    <hyperlink ref="AK170" r:id="rId11" xr:uid="{604FAE38-7BDC-4FFF-A70B-FB5BF5B2A8B1}"/>
-    <hyperlink ref="AH170" r:id="rId12" xr:uid="{0D14BE12-3694-46AE-A081-C4913693A642}"/>
-    <hyperlink ref="AI170" r:id="rId13" xr:uid="{CB3366BE-F0C6-42E0-9345-F520CF905A7B}"/>
-    <hyperlink ref="AH173" r:id="rId14" xr:uid="{6C8099A4-A7A1-4497-A789-6AF9D0BA5BDB}"/>
-    <hyperlink ref="AH174" r:id="rId15" xr:uid="{09505B9B-F457-4DB0-A57A-3B6C17F65BAE}"/>
-    <hyperlink ref="AI190" r:id="rId16" xr:uid="{B9710AAF-9B37-404F-A976-903D18F8F57B}"/>
-    <hyperlink ref="AJ190" r:id="rId17" xr:uid="{4E731BCE-C3F7-484A-9B2A-46B11C1AAAB0}"/>
-    <hyperlink ref="AH166" r:id="rId18" xr:uid="{CA8BBEE4-F576-4ABA-9568-AC20CB59BF35}"/>
-    <hyperlink ref="AH179" r:id="rId19" xr:uid="{BEC06E08-495B-478D-8834-CAF224F05E75}"/>
-    <hyperlink ref="AH185" r:id="rId20" xr:uid="{B1E3DA1E-2865-4610-AE45-EE473804C289}"/>
-    <hyperlink ref="AH181" r:id="rId21" xr:uid="{51DDC235-0C4B-44EE-801E-498C749B6D15}"/>
-    <hyperlink ref="AI188" r:id="rId22" xr:uid="{5BDA0124-CD93-42F6-86D0-392B7ABD35C5}"/>
-    <hyperlink ref="AH192" r:id="rId23" xr:uid="{3BA9C1B9-A93C-404A-8B08-C69E4387DC6D}"/>
-    <hyperlink ref="AI192" r:id="rId24" xr:uid="{020E40C3-252D-4E60-B993-F7CF4432D5AE}"/>
-    <hyperlink ref="AJ192" r:id="rId25" xr:uid="{73712456-839E-45A8-AE9E-44D79C0F39BF}"/>
-    <hyperlink ref="AH186" r:id="rId26" xr:uid="{0747EB5C-708B-48EB-AB2A-959A09A608B1}"/>
-    <hyperlink ref="AI186" r:id="rId27" xr:uid="{22F267F2-41BE-4BF3-BD3C-29EED9B76EA0}"/>
-    <hyperlink ref="AH176" r:id="rId28" xr:uid="{D9235B68-7816-4CC3-9093-B978BB854F23}"/>
-    <hyperlink ref="AI176" r:id="rId29" xr:uid="{EDD9DD06-6D5A-4AB8-AFBF-27D554CA729E}"/>
-    <hyperlink ref="AH172" r:id="rId30" xr:uid="{702DEA58-5D24-444C-9F18-C00C014762B5}"/>
-    <hyperlink ref="AI172" r:id="rId31" location="18-Statistical-processing-17" xr:uid="{2CC7A350-C221-40C2-BF31-D7B042D41B0B}"/>
-    <hyperlink ref="AK172" r:id="rId32" location="18-Statistical-processing-17" xr:uid="{93F1DBFF-7A3B-4B29-A088-1E0EC20C782D}"/>
-    <hyperlink ref="AH191" r:id="rId33" xr:uid="{747BB282-14A2-49AF-B67A-7B969618FE26}"/>
-    <hyperlink ref="AI191" r:id="rId34" xr:uid="{55FF2876-E8C0-4240-AAF0-F61CDA092B5C}"/>
-    <hyperlink ref="AJ191" r:id="rId35" xr:uid="{A78350D1-9D80-4966-9381-406E1F15388A}"/>
-    <hyperlink ref="AK191" r:id="rId36" xr:uid="{E19C6183-3E90-4595-8893-AD5693A99291}"/>
-    <hyperlink ref="AI168" r:id="rId37" xr:uid="{DB070CA9-97C5-426A-BE11-CEF9FC65BFED}"/>
-    <hyperlink ref="AJ168" r:id="rId38" xr:uid="{F82B79FE-5FE3-43AA-AB23-E8B0ED23A725}"/>
-    <hyperlink ref="AH168" r:id="rId39" xr:uid="{04D7458B-63DE-4999-9D63-FF44159961BC}"/>
-    <hyperlink ref="AH184" r:id="rId40" xr:uid="{635C077B-7FEA-44CA-8F20-11901AD73AA2}"/>
-    <hyperlink ref="AH175" r:id="rId41" xr:uid="{2419542F-8E77-4711-938A-3073FAB164D3}"/>
-    <hyperlink ref="AI175" r:id="rId42" xr:uid="{AF98DF13-1FC2-40B4-BCCE-36F73FBD48D0}"/>
-    <hyperlink ref="AJ175" r:id="rId43" xr:uid="{1075B4F9-1706-46B1-9C2C-4B791300B8A3}"/>
-    <hyperlink ref="AK175" r:id="rId44" xr:uid="{AF58B4B9-B6E6-47EC-841B-79501F4F10D6}"/>
-    <hyperlink ref="AL175" r:id="rId45" xr:uid="{6D98C45A-F7C8-457F-BFAA-40BF8721237F}"/>
-    <hyperlink ref="AI193" r:id="rId46" xr:uid="{92015F75-FEA9-43AE-89D4-87CB709894B9}"/>
-    <hyperlink ref="AJ193" r:id="rId47" xr:uid="{DC1B17C4-0CF6-46C3-8C96-E4E76EA868CA}"/>
-    <hyperlink ref="AH193" r:id="rId48" xr:uid="{05CB0796-E149-4477-8C35-ECCA3A9D48D7}"/>
-    <hyperlink ref="AH151" r:id="rId49" xr:uid="{5038DB18-E423-483B-8A62-45D0831DE591}"/>
-    <hyperlink ref="AI151" r:id="rId50" xr:uid="{0838832B-FEFA-4FCC-AEA6-B63606D85C70}"/>
-    <hyperlink ref="AH152" r:id="rId51" xr:uid="{0C573C17-792C-4968-A63C-0D9A3CC360B6}"/>
-    <hyperlink ref="AI152" r:id="rId52" xr:uid="{5538D8B7-FEB3-4EC0-8CE9-D0ACC4E8BEFF}"/>
-    <hyperlink ref="AH153" r:id="rId53" xr:uid="{90645A26-814E-4795-AEDF-74557CDDE938}"/>
-    <hyperlink ref="AH154" r:id="rId54" xr:uid="{B5FAB193-4C6D-441B-8A53-39F37A0D88E7}"/>
-    <hyperlink ref="AH155" r:id="rId55" xr:uid="{F84F20BC-3F7F-46B2-8AD9-1968E85959AD}"/>
-    <hyperlink ref="AI155" r:id="rId56" xr:uid="{A1330DEF-8B68-47ED-825F-AE56F0D0808F}"/>
-    <hyperlink ref="AH156" r:id="rId57" xr:uid="{735C2864-C62E-4EB1-9B3F-EA575925D11D}"/>
-    <hyperlink ref="AH158" r:id="rId58" xr:uid="{CDC62339-8A0E-4036-99F6-9F1450E22F12}"/>
-    <hyperlink ref="AI158" r:id="rId59" location="!/view/en/VBD_SLOVSTAT/nu2056rs/v_nu2056rs_00_00_00_en" xr:uid="{320901C4-220A-43A4-BEE2-DE41D15FB36C}"/>
-    <hyperlink ref="AH162" r:id="rId60" xr:uid="{AE2A46E1-3B3B-4BD3-B4B3-6A636E3B061C}"/>
-    <hyperlink ref="AI163" r:id="rId61" xr:uid="{23B60EA1-B711-4C60-B065-F9FA7E87E70E}"/>
-    <hyperlink ref="AH167" r:id="rId62" location="microdonn_es__content_bfs_fr_home_statistiken_industrie-dienstleistungen_erhebungen_statent_jcr_content_par_tabs" xr:uid="{D8DB0FD3-F2D7-4EE9-803F-7FDB9E9A6D6A}"/>
-    <hyperlink ref="AI167" r:id="rId63" xr:uid="{9B1B52B6-52C7-4C6B-940F-A16A7852B10D}"/>
-    <hyperlink ref="AJ172" r:id="rId64" xr:uid="{AC3443B3-72F2-4579-AC41-B405F0AC6A8C}"/>
-    <hyperlink ref="AI173" r:id="rId65" xr:uid="{4AF94ECA-DB73-459D-9D19-6A4C5BC6C230}"/>
-    <hyperlink ref="AJ176" r:id="rId66" xr:uid="{532D06F3-FEB2-431D-938E-0809C9FA04A6}"/>
-    <hyperlink ref="AI177" r:id="rId67" xr:uid="{5D024205-C977-4E77-B461-CA169F90C4EE}"/>
-    <hyperlink ref="AH180" r:id="rId68" xr:uid="{53D7F884-561D-4927-B488-3D0EB87F7174}"/>
-    <hyperlink ref="AI180" r:id="rId69" xr:uid="{8B8B3ECC-F894-4273-B242-71EF5CD12A5A}"/>
-    <hyperlink ref="AJ180" r:id="rId70" xr:uid="{70D764AB-0E37-4EA9-B463-6AF1AF36D941}"/>
-    <hyperlink ref="AH182" r:id="rId71" xr:uid="{8B9D5A42-E314-4449-A708-F86B8C639BBA}"/>
-    <hyperlink ref="AH183" r:id="rId72" xr:uid="{C54C6A2B-1B64-47A1-9AF5-4DA2C74A62FB}"/>
-    <hyperlink ref="AI184" r:id="rId73" xr:uid="{048C8F4A-3ED3-4BB0-BA5E-C9A8DB19BA08}"/>
-    <hyperlink ref="AJ184" r:id="rId74" xr:uid="{2BD3B022-1099-4E72-9E68-6AC0299867FB}"/>
-    <hyperlink ref="AK184" r:id="rId75" xr:uid="{737B47E6-EB48-4460-BA3E-1C80785081DB}"/>
-    <hyperlink ref="AL184" r:id="rId76" xr:uid="{D57CED31-746C-45D7-AAAB-F188F0C04A22}"/>
-    <hyperlink ref="AJ185" r:id="rId77" location="/CBS/nl/dataset/81238ned/table?ts=1600888891095" xr:uid="{9F548DAF-DA1D-4450-99A1-1EB091F67507}"/>
-    <hyperlink ref="AJ186" r:id="rId78" xr:uid="{8790F5D1-5DA7-4B3C-8510-3C55238421B2}"/>
-    <hyperlink ref="AH188" r:id="rId79" display="https://ec.europa.eu/eurostat/cache/metadata/EN/sbs_esms_pt.htm" xr:uid="{81994A69-4462-42C8-8451-DC4CAC1F3750}"/>
-    <hyperlink ref="AH190" r:id="rId80" xr:uid="{075F987E-A35C-4182-9947-67D4EE48AD1D}"/>
-    <hyperlink ref="AK190" r:id="rId81" xr:uid="{0A1F68C7-DCF0-4B70-84F7-258E12132163}"/>
-    <hyperlink ref="AK192" r:id="rId82" xr:uid="{A5F73C74-051A-431A-A3DB-E28F207A95D2}"/>
-    <hyperlink ref="AH165" r:id="rId83" xr:uid="{339CBE1F-A0E3-4640-9F2F-47C5DB49A10E}"/>
-    <hyperlink ref="AH178" r:id="rId84" xr:uid="{556D98EF-43F0-48AC-9365-109DCBB04810}"/>
-    <hyperlink ref="AI178" r:id="rId85" xr:uid="{F2D810C3-3682-4582-AD33-75A27B96B0D6}"/>
-    <hyperlink ref="AR162" r:id="rId86" xr:uid="{569D496B-D043-4D18-9C14-EFEE80C30B7E}"/>
-    <hyperlink ref="AI166" r:id="rId87" xr:uid="{26F5B7EB-A24D-4FF2-A158-0EC97C5E99F2}"/>
-    <hyperlink ref="AJ166" r:id="rId88" xr:uid="{9FD1B3DA-2448-4BDA-A12D-3BE998D3134A}"/>
-    <hyperlink ref="AH169" r:id="rId89" xr:uid="{D7A7DA82-4682-44B1-859A-568315A68AAE}"/>
-    <hyperlink ref="AM180" r:id="rId90" xr:uid="{7325765A-B0C5-4A8E-BE05-678B8360AB5C}"/>
-    <hyperlink ref="AJ183" r:id="rId91" xr:uid="{A5642F57-7B99-45FE-BF20-E49566815799}"/>
-    <hyperlink ref="AI183" r:id="rId92" xr:uid="{4808868F-986C-41D8-88CE-5E8207ACB7CF}"/>
-    <hyperlink ref="AL192" r:id="rId93" xr:uid="{AB002466-274D-4A60-A7FE-1C1CD2D9FB03}"/>
+    <hyperlink ref="AI149" r:id="rId1" xr:uid="{52AC0ED7-7648-40F7-B571-616312535AAA}"/>
+    <hyperlink ref="AI157" r:id="rId2" xr:uid="{45571AB8-A194-4CB5-B86F-42770FE8F0EC}"/>
+    <hyperlink ref="AM190" r:id="rId3" xr:uid="{E1B26233-1D7F-4B6E-A7B3-316AF4DFD64D}"/>
+    <hyperlink ref="AJ185" r:id="rId4" xr:uid="{865742E7-BC6D-48C2-8AD9-20E9F8A9CB8D}"/>
+    <hyperlink ref="AJ187" r:id="rId5" xr:uid="{87635245-1906-4D40-9B72-2665339404C6}"/>
+    <hyperlink ref="AI161" r:id="rId6" xr:uid="{2BBA1E7B-3597-451D-BB1B-DA7942019B4E}"/>
+    <hyperlink ref="AI189" r:id="rId7" xr:uid="{5F662825-2BB5-45A8-B790-BE007838E78C}"/>
+    <hyperlink ref="AI177" r:id="rId8" xr:uid="{D5E1BC65-C3C1-4385-AF10-90A6F6274C3D}"/>
+    <hyperlink ref="AI163" r:id="rId9" location="documents" xr:uid="{56A02F04-D2F7-469A-87C0-53B8348EFE61}"/>
+    <hyperlink ref="AK170" r:id="rId10" xr:uid="{EB7D60BA-0955-4550-B994-AEEAFCFB73F9}"/>
+    <hyperlink ref="AL170" r:id="rId11" xr:uid="{604FAE38-7BDC-4FFF-A70B-FB5BF5B2A8B1}"/>
+    <hyperlink ref="AI170" r:id="rId12" xr:uid="{0D14BE12-3694-46AE-A081-C4913693A642}"/>
+    <hyperlink ref="AJ170" r:id="rId13" xr:uid="{CB3366BE-F0C6-42E0-9345-F520CF905A7B}"/>
+    <hyperlink ref="AI173" r:id="rId14" xr:uid="{6C8099A4-A7A1-4497-A789-6AF9D0BA5BDB}"/>
+    <hyperlink ref="AI174" r:id="rId15" xr:uid="{09505B9B-F457-4DB0-A57A-3B6C17F65BAE}"/>
+    <hyperlink ref="AJ190" r:id="rId16" xr:uid="{B9710AAF-9B37-404F-A976-903D18F8F57B}"/>
+    <hyperlink ref="AK190" r:id="rId17" xr:uid="{4E731BCE-C3F7-484A-9B2A-46B11C1AAAB0}"/>
+    <hyperlink ref="AI166" r:id="rId18" xr:uid="{CA8BBEE4-F576-4ABA-9568-AC20CB59BF35}"/>
+    <hyperlink ref="AI179" r:id="rId19" xr:uid="{BEC06E08-495B-478D-8834-CAF224F05E75}"/>
+    <hyperlink ref="AI185" r:id="rId20" xr:uid="{B1E3DA1E-2865-4610-AE45-EE473804C289}"/>
+    <hyperlink ref="AI181" r:id="rId21" xr:uid="{51DDC235-0C4B-44EE-801E-498C749B6D15}"/>
+    <hyperlink ref="AJ188" r:id="rId22" xr:uid="{5BDA0124-CD93-42F6-86D0-392B7ABD35C5}"/>
+    <hyperlink ref="AI192" r:id="rId23" xr:uid="{3BA9C1B9-A93C-404A-8B08-C69E4387DC6D}"/>
+    <hyperlink ref="AJ192" r:id="rId24" xr:uid="{020E40C3-252D-4E60-B993-F7CF4432D5AE}"/>
+    <hyperlink ref="AK192" r:id="rId25" xr:uid="{73712456-839E-45A8-AE9E-44D79C0F39BF}"/>
+    <hyperlink ref="AI186" r:id="rId26" xr:uid="{0747EB5C-708B-48EB-AB2A-959A09A608B1}"/>
+    <hyperlink ref="AJ186" r:id="rId27" xr:uid="{22F267F2-41BE-4BF3-BD3C-29EED9B76EA0}"/>
+    <hyperlink ref="AI176" r:id="rId28" xr:uid="{D9235B68-7816-4CC3-9093-B978BB854F23}"/>
+    <hyperlink ref="AJ176" r:id="rId29" xr:uid="{EDD9DD06-6D5A-4AB8-AFBF-27D554CA729E}"/>
+    <hyperlink ref="AI172" r:id="rId30" xr:uid="{702DEA58-5D24-444C-9F18-C00C014762B5}"/>
+    <hyperlink ref="AJ172" r:id="rId31" location="18-Statistical-processing-17" xr:uid="{2CC7A350-C221-40C2-BF31-D7B042D41B0B}"/>
+    <hyperlink ref="AL172" r:id="rId32" location="18-Statistical-processing-17" xr:uid="{93F1DBFF-7A3B-4B29-A088-1E0EC20C782D}"/>
+    <hyperlink ref="AI191" r:id="rId33" xr:uid="{747BB282-14A2-49AF-B67A-7B969618FE26}"/>
+    <hyperlink ref="AJ191" r:id="rId34" xr:uid="{55FF2876-E8C0-4240-AAF0-F61CDA092B5C}"/>
+    <hyperlink ref="AK191" r:id="rId35" xr:uid="{A78350D1-9D80-4966-9381-406E1F15388A}"/>
+    <hyperlink ref="AL191" r:id="rId36" xr:uid="{E19C6183-3E90-4595-8893-AD5693A99291}"/>
+    <hyperlink ref="AJ168" r:id="rId37" xr:uid="{DB070CA9-97C5-426A-BE11-CEF9FC65BFED}"/>
+    <hyperlink ref="AK168" r:id="rId38" xr:uid="{F82B79FE-5FE3-43AA-AB23-E8B0ED23A725}"/>
+    <hyperlink ref="AI168" r:id="rId39" xr:uid="{04D7458B-63DE-4999-9D63-FF44159961BC}"/>
+    <hyperlink ref="AI184" r:id="rId40" xr:uid="{635C077B-7FEA-44CA-8F20-11901AD73AA2}"/>
+    <hyperlink ref="AI175" r:id="rId41" xr:uid="{2419542F-8E77-4711-938A-3073FAB164D3}"/>
+    <hyperlink ref="AJ175" r:id="rId42" xr:uid="{AF98DF13-1FC2-40B4-BCCE-36F73FBD48D0}"/>
+    <hyperlink ref="AK175" r:id="rId43" xr:uid="{1075B4F9-1706-46B1-9C2C-4B791300B8A3}"/>
+    <hyperlink ref="AL175" r:id="rId44" xr:uid="{AF58B4B9-B6E6-47EC-841B-79501F4F10D6}"/>
+    <hyperlink ref="AM175" r:id="rId45" xr:uid="{6D98C45A-F7C8-457F-BFAA-40BF8721237F}"/>
+    <hyperlink ref="AJ193" r:id="rId46" xr:uid="{92015F75-FEA9-43AE-89D4-87CB709894B9}"/>
+    <hyperlink ref="AK193" r:id="rId47" xr:uid="{DC1B17C4-0CF6-46C3-8C96-E4E76EA868CA}"/>
+    <hyperlink ref="AI193" r:id="rId48" xr:uid="{05CB0796-E149-4477-8C35-ECCA3A9D48D7}"/>
+    <hyperlink ref="AI151" r:id="rId49" xr:uid="{5038DB18-E423-483B-8A62-45D0831DE591}"/>
+    <hyperlink ref="AJ151" r:id="rId50" xr:uid="{0838832B-FEFA-4FCC-AEA6-B63606D85C70}"/>
+    <hyperlink ref="AI152" r:id="rId51" xr:uid="{0C573C17-792C-4968-A63C-0D9A3CC360B6}"/>
+    <hyperlink ref="AJ152" r:id="rId52" xr:uid="{5538D8B7-FEB3-4EC0-8CE9-D0ACC4E8BEFF}"/>
+    <hyperlink ref="AI153" r:id="rId53" xr:uid="{90645A26-814E-4795-AEDF-74557CDDE938}"/>
+    <hyperlink ref="AI154" r:id="rId54" xr:uid="{B5FAB193-4C6D-441B-8A53-39F37A0D88E7}"/>
+    <hyperlink ref="AI155" r:id="rId55" xr:uid="{F84F20BC-3F7F-46B2-8AD9-1968E85959AD}"/>
+    <hyperlink ref="AJ155" r:id="rId56" xr:uid="{A1330DEF-8B68-47ED-825F-AE56F0D0808F}"/>
+    <hyperlink ref="AI156" r:id="rId57" xr:uid="{735C2864-C62E-4EB1-9B3F-EA575925D11D}"/>
+    <hyperlink ref="AI158" r:id="rId58" xr:uid="{CDC62339-8A0E-4036-99F6-9F1450E22F12}"/>
+    <hyperlink ref="AJ158" r:id="rId59" location="!/view/en/VBD_SLOVSTAT/nu2056rs/v_nu2056rs_00_00_00_en" xr:uid="{320901C4-220A-43A4-BEE2-DE41D15FB36C}"/>
+    <hyperlink ref="AI162" r:id="rId60" xr:uid="{AE2A46E1-3B3B-4BD3-B4B3-6A636E3B061C}"/>
+    <hyperlink ref="AJ163" r:id="rId61" xr:uid="{23B60EA1-B711-4C60-B065-F9FA7E87E70E}"/>
+    <hyperlink ref="AI167" r:id="rId62" location="microdonn_es__content_bfs_fr_home_statistiken_industrie-dienstleistungen_erhebungen_statent_jcr_content_par_tabs" xr:uid="{D8DB0FD3-F2D7-4EE9-803F-7FDB9E9A6D6A}"/>
+    <hyperlink ref="AJ167" r:id="rId63" xr:uid="{9B1B52B6-52C7-4C6B-940F-A16A7852B10D}"/>
+    <hyperlink ref="AK172" r:id="rId64" xr:uid="{AC3443B3-72F2-4579-AC41-B405F0AC6A8C}"/>
+    <hyperlink ref="AJ173" r:id="rId65" xr:uid="{4AF94ECA-DB73-459D-9D19-6A4C5BC6C230}"/>
+    <hyperlink ref="AK176" r:id="rId66" xr:uid="{532D06F3-FEB2-431D-938E-0809C9FA04A6}"/>
+    <hyperlink ref="AJ177" r:id="rId67" xr:uid="{5D024205-C977-4E77-B461-CA169F90C4EE}"/>
+    <hyperlink ref="AI180" r:id="rId68" xr:uid="{53D7F884-561D-4927-B488-3D0EB87F7174}"/>
+    <hyperlink ref="AJ180" r:id="rId69" xr:uid="{8B8B3ECC-F894-4273-B242-71EF5CD12A5A}"/>
+    <hyperlink ref="AK180" r:id="rId70" xr:uid="{70D764AB-0E37-4EA9-B463-6AF1AF36D941}"/>
+    <hyperlink ref="AI182" r:id="rId71" xr:uid="{8B9D5A42-E314-4449-A708-F86B8C639BBA}"/>
+    <hyperlink ref="AI183" r:id="rId72" xr:uid="{C54C6A2B-1B64-47A1-9AF5-4DA2C74A62FB}"/>
+    <hyperlink ref="AJ184" r:id="rId73" xr:uid="{048C8F4A-3ED3-4BB0-BA5E-C9A8DB19BA08}"/>
+    <hyperlink ref="AK184" r:id="rId74" xr:uid="{2BD3B022-1099-4E72-9E68-6AC0299867FB}"/>
+    <hyperlink ref="AL184" r:id="rId75" xr:uid="{737B47E6-EB48-4460-BA3E-1C80785081DB}"/>
+    <hyperlink ref="AM184" r:id="rId76" xr:uid="{D57CED31-746C-45D7-AAAB-F188F0C04A22}"/>
+    <hyperlink ref="AK185" r:id="rId77" location="/CBS/nl/dataset/81238ned/table?ts=1600888891095" xr:uid="{9F548DAF-DA1D-4450-99A1-1EB091F67507}"/>
+    <hyperlink ref="AK186" r:id="rId78" xr:uid="{8790F5D1-5DA7-4B3C-8510-3C55238421B2}"/>
+    <hyperlink ref="AI188" r:id="rId79" display="https://ec.europa.eu/eurostat/cache/metadata/EN/sbs_esms_pt.htm" xr:uid="{81994A69-4462-42C8-8451-DC4CAC1F3750}"/>
+    <hyperlink ref="AI190" r:id="rId80" xr:uid="{075F987E-A35C-4182-9947-67D4EE48AD1D}"/>
+    <hyperlink ref="AL190" r:id="rId81" xr:uid="{0A1F68C7-DCF0-4B70-84F7-258E12132163}"/>
+    <hyperlink ref="AL192" r:id="rId82" xr:uid="{A5F73C74-051A-431A-A3DB-E28F207A95D2}"/>
+    <hyperlink ref="AI165" r:id="rId83" xr:uid="{339CBE1F-A0E3-4640-9F2F-47C5DB49A10E}"/>
+    <hyperlink ref="AI178" r:id="rId84" xr:uid="{556D98EF-43F0-48AC-9365-109DCBB04810}"/>
+    <hyperlink ref="AJ178" r:id="rId85" xr:uid="{F2D810C3-3682-4582-AD33-75A27B96B0D6}"/>
+    <hyperlink ref="AS162" r:id="rId86" xr:uid="{569D496B-D043-4D18-9C14-EFEE80C30B7E}"/>
+    <hyperlink ref="AJ166" r:id="rId87" xr:uid="{26F5B7EB-A24D-4FF2-A158-0EC97C5E99F2}"/>
+    <hyperlink ref="AK166" r:id="rId88" xr:uid="{9FD1B3DA-2448-4BDA-A12D-3BE998D3134A}"/>
+    <hyperlink ref="AI169" r:id="rId89" xr:uid="{D7A7DA82-4682-44B1-859A-568315A68AAE}"/>
+    <hyperlink ref="AN180" r:id="rId90" xr:uid="{7325765A-B0C5-4A8E-BE05-678B8360AB5C}"/>
+    <hyperlink ref="AK183" r:id="rId91" xr:uid="{A5642F57-7B99-45FE-BF20-E49566815799}"/>
+    <hyperlink ref="AJ183" r:id="rId92" xr:uid="{4808868F-986C-41D8-88CE-5E8207ACB7CF}"/>
+    <hyperlink ref="AM192" r:id="rId93" xr:uid="{AB002466-274D-4A60-A7FE-1C1CD2D9FB03}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId94"/>
@@ -47166,15 +47400,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ADB9CD767C4FF34281D6635032C5B89D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3b7ad1acb7d07f4c67b79ea712f2c443">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b19ad29f-88fa-4d62-ac16-34b992563bf9" xmlns:ns3="e781ea9d-1795-4792-8d8d-c86ae526af93" xmlns:ns4="3e02667f-0271-471b-bd6e-11a2e16def1d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e0bd56705adf4bb69ae57d53dbdc9cd2" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
@@ -47422,6 +47647,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -47434,14 +47668,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8001F0D6-2591-4A68-815D-C98503A36C32}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64F7F7F6-A9CF-4163-97CB-3D814FACF000}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47461,13 +47687,28 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8001F0D6-2591-4A68-815D-C98503A36C32}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACEEE91F-8CDF-4F2C-85D3-58EC881B6941}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>